--- a/output/pms/Lập_trình_Python/Session 02 - Môi trường Python 3.12 và Cú pháp cơ bản/Session02._Quizz_Dau_Gio_Tổng_quan_về_ngôn_ngữ_Python_3_12.xlsx
+++ b/output/pms/Lập_trình_Python/Session 02 - Môi trường Python 3.12 và Cú pháp cơ bản/Session02._Quizz_Dau_Gio_Tổng_quan_về_ngôn_ngữ_Python_3_12.xlsx
@@ -539,51 +539,51 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Khi phát triển ứng dụng quản lý thông tin trong Python 3.12, lập trình viên cần tạo một biến để lưu trữ tổng số lượng đơn hàng của hệ thống. Theo quy tắc đặt tên biến chuẩn mực PEP 8 và cú pháp hợp lệ của Python, đâu là cách khai báo biến chính xác?</t>
+          <t>Khi khởi tạo biến để lưu trữ điểm số của học viên trong Python 3.12, câu lệnh nào dưới đây tuân thủ đúng quy tắc đặt tên định danh (identifier) và cú pháp khai báo biến?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>`class = 150`</t>
+          <t>Sử dụng cú pháp ```class = 95``` để lưu trữ giá trị với tên biến trùng với từ khóa hệ thống có sẵn.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Phương án `class = 150` sai vì `class` là một từ khóa dự trữ (reserved keyword) được dùng để định nghĩa lớp trong Python. Lập trình viên không được sử dụng từ khóa dự trữ của ngôn ngữ để đặt tên biến.</t>
+          <t>Từ khóa ```class``` là từ khóa reserved dành riêng của ngôn ngữ Python, không được phép sử dụng làm tên biến đặt tự do.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>`150_total_orders = 150`</t>
+          <t>Sử dụng cú pháp ```1st_student_score = 95``` để lưu trữ giá trị với tên biến bắt đầu bằng một chữ số nguyên.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Phương án `150_total_orders = 150` sai vì quy tắc cú pháp cơ bản của Python không cho phép tên biến bắt đầu bằng một chữ số (`150`). Trình biên dịch Python sẽ báo lỗi `SyntaxError` ngay khi khởi chạy.</t>
+          <t>Cú pháp này vi phạm quy tắc đặt tên biến trong Python do cấm tên biến bắt đầu bằng chữ số, dẫn đến lỗi cú pháp SyntaxError.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>`total_order_count = 150`</t>
+          <t>Sử dụng cú pháp ```student-score = 95``` để lưu trữ giá trị với tên biến chứa ký tự dấu gạch ngang.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Phương án `total_order_count = 150` hoàn toàn chính xác. Tên biến tuân thủ đúng quy tắc PEP 8 (`snake_case`): chỉ bao gồm các chữ cái viết thường, phân cách các từ bằng dấu gạch dưới, không bắt đầu bằng số và không trùng với từ khóa hệ thống.</t>
+          <t>Dấu gạch ngang (-) được trình biên dịch Python hiểu là toán tử trừ số học, không thể dùng làm một phần tên của biến.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>`total-order-count = 150`</t>
+          <t>Sử dụng cú pháp ```student_score = 95``` để lưu trữ giá trị với tên biến gồm chữ cái và dấu gạch dưới hợp lệ.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Phương án `total-order-count = 150` sai vì ký tự dấu gạch ngang (`-`) được Python hiểu là toán tử trừ. Trình biên dịch sẽ nhận diện đây là một phép toán chứ không phải tên biến hợp lệ, dẫn đến lỗi `SyntaxError`.</t>
+          <t>Trong Python 3.12, tên biến hợp lệ phải bắt đầu bằng một chữ cái hoặc dấu gạch dưới (_), không được bắt đầu bằng chữ số, không chứa ký tự đặc biệt như dấu gạch ngang và không trùng với từ khóa hệ thống.</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>4</v>
@@ -600,54 +600,47 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Giả sử bạn thực thi đoạn mã Python 3.12 hiển thị thông tin sản phẩm bằng kỹ thuật định dạng chuỗi f-string như sau:
-```python
-product_name = "Laptop"
-product_price = 1200.5
-output_message = f"Sản phẩm {product_name} có giá: {product_price:.2f}$"
-print(output_message)
-```
-Kết quả in ra trên màn hình console là gì?</t>
+          <t>Trong ứng dụng console tương tác, hàm ```input()``` nhận dữ liệu từ người dùng dưới dạng chuỗi ký tự. Khi người dùng nhập chuỗi ```"25"```, đoạn mã nào thực hiện đọc dữ liệu và chuyển đổi thành kiểu số nguyên (```int```) đúng cú pháp?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>`Sản phẩm "Laptop" có giá: 1200.50$`</t>
+          <t>Sử dụng câu lệnh ```user_age = parse_int(input())``` để gọi hàm giải mã số nguyên từ dữ liệu đầu vào.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Phương án `Sản phẩm "Laptop" có giá: 1200.50$` sai vì khi nội suy biến chuỗi `{product_name}` vào f-string, Python chỉ lấy giá trị nội dung văn bản bên trong là `Laptop` chứ không tự động bao bọc thêm cặp dấu nháy kép `""`.</t>
+          <t>Trong Python không tồn tại hàm built-in tên là ```parse_int()``` để phục vụ chuyển đổi kiểu dữ liệu.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>`Sản phẩm product_name có giá: product_price$`</t>
+          <t>Sử dụng câu lệnh ```user_age = input(int)``` để truyền từ khóa kiểu dữ liệu ```int``` trực tiếp vào hàm ```input()```.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Phương án `Sản phẩm product_name có giá: product_price$` sai vì học viên nhầm f-string với chuỗi văn bản thông thường. Ký tự `f` trước chuỗi yêu cầu Python phải nội suy và thay thế các biểu thức bên trong ngoặc nhọn `{}` bằng giá trị của biến.</t>
+          <t>Hàm ```input()``` chỉ nhận tham số là một chuỗi dùng làm dòng thông báo (prompt), không nhận kiểu dữ liệu để tự động chuyển kiểu.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>`Sản phẩm Laptop có giá: 1200.50$`</t>
+          <t>Sử dụng câu lệnh ```user_age = int(input())``` để bọc hàm ```input()``` bên trong hàm chuyển kiểu ```int()```.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Phương án `Sản phẩm Laptop có giá: 1200.50$` đúng. Trong f-string của Python 3.12, cú pháp định dạng `{product_price:.2f}` sẽ quy đổi giá trị số thực `1200.5` thành chuỗi hiển thị đúng 2 chữ số sau phần thập phân, do đó kết quả được bù thêm số 0 thành `1200.50`.</t>
+          <t>Hàm ```input()``` luôn trả về dữ liệu kiểu chuỗi (```str```). Để chuyển đổi chuỗi chữ số thu được thành số nguyên, cần truyền giá trị trả về của ```input()``` làm đối số cho hàm ép kiểu ```int()```.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>`Sản phẩm Laptop có giá: 1200.5$`</t>
+          <t>Sử dụng câu lệnh ```user_age = str(input())``` để bọc hàm ```input()``` bên trong hàm chuyển kiểu ```str()```.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Phương án `Sản phẩm Laptop có giá: 1200.5$` sai vì học viên nhầm lẫn rằng định dạng `.2f` sẽ giữ nguyên chữ số thập phân sẵn có của biến mà không tự động thêm chữ số `0` cho đủ 2 chữ số phần thập phân.</t>
+          <t>Hàm ```str()``` chỉ duy trì hoặc chuyển đổi dữ liệu thành kiểu chuỗi ký tự, không thể biến đổi chuỗi ```"25"``` thành số nguyên kiểu ```int```.</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -668,57 +661,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 thực hiện việc chuyển đổi kiểu dữ liệu cơ bản và xuất thông tin kiểu dữ liệu ra màn hình console như sau:
-```python
-raw_point = "95"
-converted_point = int(raw_point)
-print(type(converted_point))
-```
-Kết quả hiển thị chính xác trên màn hình console sau khi thực thi là gì?</t>
+          <t>Khi thực thi câu lệnh khai báo biến ```is_active = True``` trong môi trường Python 3.12, việc kiểm tra kiểu dữ liệu thông qua lệnh ```print(type(is_active))``` sẽ trả về kết quả nào trên màn hình console?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'int'&gt;`</t>
+          <t>Kết quả xuất ra màn hình là ```&lt;class 'str'&gt;``` xác định kiểu dữ liệu chuỗi văn bản bản địa.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Phương án `&lt;class 'int'&gt;` đúng. Hàm `int(raw_point)` chuyển đổi thành công chuỗi ký tự `"95"` thành số nguyên `95`. Hàm `type()` trong Python luôn trả về thông tin kiểu dữ liệu dưới dạng đại diện lớp `&lt;class 'int'&gt;`.</t>
+          <t>Giá trị ```True``` không được đặt trong cặp dấu bao chuỗi, do đó nó không phải là kiểu chuỗi ký tự ```str```.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>`int`</t>
+          <t>Kết quả xuất ra màn hình là ```&lt;class 'boolean'&gt;``` xác định tên kiểu dữ liệu nguyên bản đầy đủ.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Phương án `int` sai về mặt định dạng đầu ra. Hàm built-in `type()` trong Python khi in ra console sẽ luôn hiển thị kèm tiền tố ngữ cảnh lớp dạng `&lt;class 'int'&gt;` chứ không chỉ trả về tên kiểu dữ liệu ngắn gọn.</t>
+          <t>Tên kiểu dữ liệu đại diện cho Boolean trong Python được quy định ngắn gọn là ```bool```, không phải ```boolean```.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'str'&gt;`</t>
+          <t>Kết quả xuất ra màn hình là ```&lt;class 'int'&gt;``` xác định kiểu dữ liệu số nguyên đại diện.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Phương án `&lt;class 'str'&gt;` sai vì đây là kiểu dữ liệu ban đầu của `raw_point` trước khi chuyển đổi. Biến `converted_point` đã nhận giá trị kết quả sau khi qua hàm `int()`, nên kiểu của nó không còn là `str`.</t>
+          <t>Mặc dù giá trị Boolean có thể chuyển đổi tương đương với số 1 hoặc 0 trong các phép tính, kiểu dữ liệu nguyên bản của biến vẫn là ```bool```.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'float'&gt;`</t>
+          <t>Kết quả xuất ra màn hình là ```&lt;class 'bool'&gt;``` xác định kiểu dữ liệu logic Boolean cơ sở.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Phương án `&lt;class 'float'&gt;` sai vì hàm `int()` thực hiện chuyển đổi dữ liệu về kiểu số nguyên (`int`). Để thu được kết quả `&lt;class 'float'&gt;`, đoạn mã phải ép kiểu bằng hàm `float(raw_point)`.</t>
+          <t>Trong Python, hai giá trị ```True``` và ```False``` thuộc kiểu dữ liệu cơ sở Boolean. Hàm built-in ```type()``` sẽ trả về thông tin lớp đại diện của kiểu dữ liệu này dưới dạng ```&lt;class 'bool'&gt;```.</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>4</v>
@@ -735,51 +722,59 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Trong Python, quy tắc đặt tên biến và chuẩn trình bày mã nguồn PEP 8 đóng vai trò rất quan trọng để đảm bảo tính nhất quán. Xét yêu cầu khai báo một biến lưu trữ số lượng người dùng hệ thống (`total_user_count`), cú pháp khai báo nào dưới đây là **đúng cú pháp Python** và **tuân thủ chuẩn PEP 8**?</t>
+          <t>Trong ngôn ngữ lập trình Python 3.12, quy tắc đặt tên biến yêu cầu tên biến không được chứa ký tự đặc biệt (ngoại trừ dấu gạch dưới `_`), không được bắt đầu bằng chữ số và không chứa khoảng trắng. Tên biến nào dưới đây khai báo đúng cú pháp để lưu trữ giá trị kiểu số thực?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>`total-user-count = 100`</t>
+          <t>```python
+2024_score_value = 88.5
+```</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Cú pháp này sai vì dấu gạch ngang (`-`) trong Python được hiểu là toán tử trừ số học. Trình phiên dịch Python sẽ hiểu câu lệnh này là phép toán `total - user - count = 100`, dẫn đến lỗi cú pháp `SyntaxError: cannot assign to expression`.</t>
+          <t>Tên biến `2024_score_value` không hợp lệ vì trong Python, tên biến tuyệt đối không được phép bắt đầu bằng chữ số.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>`total_user_count = 100`</t>
+          <t>```python
+score-value-2024 = 88.5
+```</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>`total_user_count = 100` hoàn toàn đúng cú pháp Python và tuân thủ chuẩn PEP 8. Chuẩn PEP 8 quy định biến thông thường nên được đặt tên theo định dạng `snake_case` (viết chữ thường, các từ phân cách bằng dấu gạch dưới `_`), vừa giúp tên biến rõ nghĩa bằng tiếng Anh vừa tránh các lỗi cú pháp.</t>
+          <t>Tên biến `score-value-2024` không hợp lệ vì chứa ký tự gạch ngang `-`, ký tự này bị trình thông dịch phân tích thành toán tử trừ.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>`total user count = 100`</t>
+          <t>```python
+_score_value_2024 = 88.5
+```</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Cú pháp này sai vì tên biến trong Python không được chứa khoảng trắng (space). Khi tách các từ bằng khoảng trắng, Python không thể nhận diện đây là một tên biến đơn lẻ và sẽ báo lỗi cú pháp `SyntaxError: invalid syntax`.</t>
+          <t>Tên biến `_score_value_2024` tuân thủ đúng quy tắc cú pháp của Python vì bắt đầu bằng dấu gạch dưới `_` và chỉ bao gồm các chữ cái, chữ số cùng dấu gạch dưới.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>`100_total_user = 100`</t>
+          <t>```python
+score value 2024 = 88.5
+```</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Cú pháp này sai vì trong Python, tên biến không được phép bắt đầu bằng một chữ số. Việc đặt `100` ở đầu tên biến sẽ khiến trình phiên dịch Python báo lỗi cú pháp `SyntaxError: invalid syntax` ngay khi thực thi.</t>
+          <t>Tên biến `score value 2024` không hợp lệ vì chứa các khoảng trắng phân tách giữa các từ, vi phạm cú pháp khai báo tên biến đơn.</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>4</v>
@@ -796,57 +791,67 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã lệnh Python xử lý dữ liệu đơn hàng dưới đây:
-```python
-item_price = "50"
-item_quantity = 2
-total_cost = item_price * item_quantity
-```
-Sau khi thực thi đoạn mã trên, giá trị và kiểu dữ liệu của biến `total_cost` thu được là gì?</t>
+          <t>Một chương trình Python 3.12 cần nhận hai số nguyên nhập từ bàn phím qua console và thực hiện tính tổng của chúng. Giả sử người dùng nhập vào lần lượt hai giá trị `10` và `20`. Đoạn mã nào dưới đây xử lý đúng để trả về kết quả số nguyên `30`?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `TypeError` vì không thể thực hiện phép nhân giữa chuỗi và số nguyên.</t>
+          <t>```python
+num1 = input()
+num2 = input()
+result = num1 + num2
+```</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Học viên dễ nhầm lẫn với toán tử cộng `+` (cộng chuỗi với số nguyên sẽ gây lỗi `TypeError`). Tuy nhiên, với toán tử nhân `*`, Python cho phép nhân chuỗi với số nguyên để lặp lại chuỗi, do đó chương trình chạy bình thường mà không phát sinh lỗi.</t>
+          <t>Hàm `input()` trả về kiểu chuỗi (`str`), nên phép cộng `+` giữa hai chuỗi `"10"` và `"20"` sẽ thực hiện thao tác nối chuỗi tạo ra kết quả `"1020"`.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Giá trị là `"5050"` và kiểu dữ liệu là `str` (chuỗi ký tự).</t>
+          <t>```python
+num1 = str(input())
+num2 = str(input())
+result = num1 + num2
+```</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Trong Python, biến `item_price` đang giữ giá trị dạng chuỗi `"50"` (`str`), còn `item_quantity` là số nguyên `2` (`int`). Khi sử dụng toán tử nhân `*` giữa một chuỗi ký tự và một số nguyên `n`, Python sẽ thực hiện thao tác lặp lại chuỗi đó `n` lần (sequence repetition). Do đó, `"50" * 2` trả về chuỗi `"5050"` với kiểu dữ liệu `str`.</t>
+          <t>Sử dụng `str(input())` giữ nguyên dữ liệu ở dạng chuỗi ký tự, do đó phép cộng `+` tiếp tục thực hiện nối chuỗi tạo ra kết quả `"1020"`.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Giá trị là `100` và kiểu dữ liệu là `int` (số nguyên).</t>
+          <t>```python
+num1 = int(input)
+num2 = int(input)
+result = num1 + num2
+```</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Đây là tư duy sai lầm khi ngầm định Python tự động chuyển đổi chuỗi `"50"` thành số `50` để tính toán số học. Trong Python, không có cơ chế tự động ép kiểu từ chuỗi chữ số sang số nguyên khi thực hiện phép nhân `*`, lập trình viên phải dùng hàm `int(item_price)` nếu muốn tính ra kết quả số nguyên `100`.</t>
+          <t>Cú pháp `int(input)` truyền đối tượng hàm `input` làm đối số cho `int()` mà không gọi hàm bằng cặp ngoặc `()`, gây ra lỗi `TypeError` khi chương trình chạy.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Giá trị là `50.0` và kiểu dữ liệu là `float` (số thực).</t>
+          <t>```python
+num1 = int(input())
+num2 = int(input())
+result = num1 + num2
+```</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai vì phép nhân giữa chuỗi `"50"` và số nguyên `2` không sinh ra số thực `float`. Toán tử nhân chuỗi tạo ra kết quả là chuỗi `"5050"`, không xảy ra phép toán chuyển đổi số thực nào.</t>
+          <t>Hàm `input()` mặc định trả về dữ liệu kiểu chuỗi (`str`). Việc bọc `int(input())` giúp chuyển đổi dữ liệu nhập vào sang số nguyên (`int`), cho phép phép cộng `+` tính toán ra tổng số học `30`.</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>4</v>
@@ -863,53 +868,52 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python kiểm tra đặc tính kiểu dữ liệu dưới đây:
+          <t>Trong Python 3.12, xét đoạn mã thực hiện khởi tạo và kiểm tra kiểu dữ liệu của biến như sau:
 ```python
-user_age = 25
-user_age = "twenty five"
-print(type(user_age))
+val_a = 10 / 2
+val_b = type(val_a)
 ```
-Kết quả hiển thị trên màn hình console khi chạy đoạn mã trên là gì và tại sao?</t>
+Biến `val_b` sẽ lưu trữ giá trị đại diện cho kiểu dữ liệu nào dưới đây?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `TypeError` do không thể gán giá trị kiểu chuỗi (`str`) cho biến đã mang kiểu số nguyên (`int`).</t>
+          <t>Kiểu `int` vì kết quả phép toán `10 / 2` là một số nguyên chẵn không chứa phần dư thập phân.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai vì Python hỗ trợ gán lại (re-assignment) bất kỳ giá trị thuộc kiểu dữ liệu nào cho một biến đã tồn tại mà không hề phát sinh lỗi kiểu `TypeError`.</t>
+          <t>Mặc dù `10` chia hết cho `2`, toán tử `/` trong Python vẫn tạo ra giá trị số thực `5.0` chứ không phải số nguyên kiểu `int`.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'int'&gt;` vì biến `user_age` đã được khởi tạo ban đầu với kiểu số nguyên và không thể thay đổi kiểu dữ liệu.</t>
+          <t>Kiểu `bool` vì phép chia thực hiện kiểm tra tính chia hết và trả về giá trị logic True/False.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Đây là tư duy sai lầm do ảnh hưởng từ các ngôn ngữ tĩnh (Static Typing) như C++ hoặc Java (nơi biến không thể đổi kiểu sau khi khai báo). Trong Python, kiểu dữ liệu gắn liền với đối tượng (giá trị) chứ không gắn liền với tên biến.</t>
+          <t>Toán tử `/` là toán tử số học dùng để tính thương, không phải toán tử quan hệ hay logic nên không trả về kiểu `bool`.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `SyntaxError` vì khai báo lại biến `user_age` đã tồn tại trong cùng phạm vi.</t>
+          <t>Kiểu `str` vì các phép tính số học tự động chuyển đổi dữ liệu đầu ra về dạng chuỗi ký tự.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Học viên nhầm lẫn với các ngôn ngữ đòi hỏi từ khóa khai báo biến riêng (như `let`/`const` trong JavaScript không cho phép khai báo lại trùng tên trong cùng một scope). Python không dùng từ khóa khai báo riêng, việc gán lại cùng một tên biến chỉ đơn giản là cập nhật tham chiếu sang giá trị mới.</t>
+          <t>Phép chia toán tử `/` tính toán trên các số nguyên và trả về số thực, không tự động chuyển đổi thành chuỗi ký tự kiểu `str`.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'str'&gt;` vì Python là ngôn ngữ có kiểu dữ liệu động (Dynamic Typing), kiểu dữ liệu của biến thay đổi theo giá trị mới nhất được gán.</t>
+          <t>Kiểu `float` vì phép chia toán tử `/` trong Python 3.12 luôn trả về kết quả thuộc kiểu số thực.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Trong Python, các biến không bị gắn chặt với một kiểu dữ liệu cố định (Dynamic Typing). Ban đầu `user_age` nhận giá trị số nguyên `25` (`int`), nhưng khi được gán lại bằng chuỗi `"twenty five"`, giá trị và kiểu dữ liệu của `user_age` tự động chuyển sang `str`. Do đó hàm `type(user_age)` trả về `&lt;class 'str'&gt;`.</t>
+          <t>Trong Python 3.12, phép chia sử dụng toán tử `/` luôn trả về kết quả thuộc kiểu số thực (`float`), kể cả khi phép chia hết (ví dụ `10 / 2` cho kết quả `5.0`). Do đó `type(val_a)` trả về `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -930,51 +934,56 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Trong Python 3.12, quy tắc PEP 8 quy định chuẩn đặt tên biến (`snake_case`) cho các biến lưu trữ thông tin cơ bản. Giả sử lập trình viên muốn khai báo một biến để lưu số tuổi của người dùng với giá trị `25`, câu lệnh nào sau đây vừa đúng cú pháp Python vừa tuân thủ chuẩn PEP 8?</t>
+          <t>Khi viết chương trình Python 3.12 thực hiện nhập dữ liệu từ console và tính toán, nhà phát triển thực thi đoạn mã sau:
+```python
+user_age = input("Nhập tuổi: ")
+result = user_age + 5
+```
+HHiện tượng nào sẽ xảy ra khi thực thi đoạn mã trên và giải pháp xử lý kỹ thuật nào là chuẩn xác?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>`user_age = 25`</t>
+          <t>Chương trình chạy thành công và xuất giá trị `25` vì Python 3.12 tự động ép kiểu chuỗi số sang kiểu số nguyên.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A đúng vì tên biến `user_age` sử dụng hoàn toàn chữ cái viết thường và phân cách các từ bằng dấu gạch dưới `_`, đúng chuẩn quy tắc `snake_case` của PEP 8. Đồng thời cú pháp gán giá trị số nguyên `25` là hoàn toàn hợp lệ trong Python.</t>
+          <t>Python là ngôn ngữ định kiểu động nhưng không tự động ép kiểu ngầm định giữa chuỗi ký tự và số nguyên trong các phép tính số học, do đó chương trình không thể tự động trả về kết quả số nguyên `25`.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>`UserAge = 25`</t>
+          <t>Chương trình báo lỗi `ValueError` vì `input()` tự động gán kiểu `float`; cần ép kiểu bằng `str(user_age) + 5`.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai về quy chuẩn phong cách PEP 8. Định dạng `UserAge` (PascalCase) trong Python được dành riêng cho quy tắc đặt tên lớp (Class), không được khuyến khích dùng cho biến thông thường dù cú pháp này không gây ra lỗi dừng chương trình.</t>
+          <t>Hàm `input()` không tự động trả về kiểu `float` và lỗi phát sinh khi thực hiện phép cộng giữa chuỗi với số nguyên là `TypeError` chứ không phải `ValueError`. Đồng thời, ép kiểu `str(user_age)` chỉ thực hiện phép nối chuỗi chứ không tính được tuổi.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>`21_user_age = 25`</t>
+          <t>Chương trình báo lỗi `TypeError` vì `input()` luôn trả về kiểu `str`; cần ép kiểu bằng `int(user_age) + 5`.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì trong Python, tên biến tuyệt đối không được bắt đầu bằng chữ số (ở đây là `21`). Khi chạy trình biên dịch Python, chương trình sẽ báo lỗi cú pháp `SyntaxError: invalid decimal literal` ngay từ bước phân tích mã nguồn.</t>
+          <t>Trong Python, hàm `input()` luôn trả về dữ liệu thuộc kiểu chuỗi (`str`). Việc sử dụng toán tử `+` giữa một chuỗi (`str`) và một số nguyên (`int`) sẽ gây ra lỗi `TypeError` do không cùng kiểu dữ liệu. Để thực hiện phép tính số học, cần ép kiểu dữ liệu đầu vào sang số nguyên bằng hàm `int()`.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>`user-age = 25`</t>
+          <t>Chương trình chạy thành công và xuất giá trị `"205"` vì Python 3.12 tự động chuyển đổi số `5` thành chuỗi ký tự.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì sử dụng dấu gạch ngang `-` (dạng kebab-case). Trong Python, trình thông dịch sẽ hiểu dấu `-` là toán tử trừ số học (`user` trừ `age`), dẫn đến lỗi `NameError` hoặc `SyntaxError` vì hai tên biến chưa được định nghĩa trước đó.</t>
+          <t>Python không tự động chuyển đổi số nguyên `5` thành chuỗi ký tự `"5"` trong phép cộng trực tiếp với chuỗi để tạo ra `"205"`, mà sẽ dừng chương trình và báo lỗi `TypeError` ngay tại thời điểm thực thi.</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>4</v>
@@ -991,56 +1000,51 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã khởi tạo các biến thông tin người chơi trong Python 3.12 như sau:
-```python
-player_name = "Alex"
-score_value = 95
-```
-Lập trình viên muốn sử dụng tính năng f-string của hàm `print()` để xuất ra màn hình nội dung chuỗi chính xác: `Player Alex scored 95 points.`. Cú pháp nào dưới đây thực hiện đúng yêu cầu trên?</t>
+          <t>Trong ngôn ngữ lập trình Python 3.12, quy tắc đặt tên biến (identifier) yêu cầu tuân thủ đúng định dạng chuẩn của ngôn ngữ. Tên biến nào sau đây là hợp lệ?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>`print(f"Player {player_name} scored {score_value} points.")`</t>
+          <t>`2024_total_user` (Hợp lệ vì Python cho phép tên biến bắt đầu bằng ký tự chữ số nguyên)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A đúng vì cú pháp f-string yêu cầu tiền tố `f` trước dấu mở ngoặc chuỗi, và các biến cần nội suy dữ liệu được đặt bên trong cặp dấu ngoặc nhọn `{}` một cách hợp lệ.</t>
+          <t>Tên biến `2024_total_user` không hợp lệ vì quy tắc cú pháp của Python nghiêm cấm tên biến bắt đầu bằng chữ số.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>`print("Player {player_name} scored {score_value} points.")`</t>
+          <t>`class` (Hợp lệ vì các từ khóa hệ thống trong Python có thể dùng làm tên biến tự do)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì thiếu tiền tố `f` ở trước chuỗi ký tự. Khi không có tiền tố `f`, hàm `print()` sẽ xử lý toàn bộ văn bản dưới dạng chuỗi thuần túy và in ra chính xác dòng chữ `Player {player_name} scored {score_value} points.` thay vì thay thế giá trị của biến.</t>
+          <t>Tên biến `class` không hợp lệ vì `class` là một từ khóa dự trữ (reserved keyword) của ngôn ngữ Python, không thể sử dụng làm tên biến đặt cho dữ liệu.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>`print(f"Player {player_name} scored {score_value points}.")`</t>
+          <t>`total_user_2024` (Hợp lệ vì bắt đầu bằng chữ cái và chỉ chứa chữ cái, chữ số, dấu gạch dưới `_`)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai về cú pháp vì bao bọc cả từ `points` vào bên trong cặp dấu ngoặc nhọn `{score_value points}`. Python sẽ hiểu `score_value points` là một biểu thức không hợp lệ và phát sinh lỗi cú pháp `SyntaxError`.</t>
+          <t>Tên biến `total_user_2024` hoàn toàn hợp lệ vì theo quy tắc cú pháp Python, tên biến phải bắt đầu bằng một chữ cái (a-z, A-Z) hoặc dấu gạch dưới `_`, các ký tự tiếp theo có thể là chữ cái, chữ số (0-9) hoặc dấu gạch dưới.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>`print(f"Player ${player_name} scored ${score_value} points.")`</t>
+          <t>`user-total-count` (Hợp lệ vì ký tự gạch nối `-` được công nhận là ký tự phân tách tên biến)</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì nhầm lẫn cú pháp nội suy của các ngôn ngữ khác (như JavaScript hoặc Bash) vốn sử dụng ký tự `$`. Trong Python f-string, ký tự `$` chỉ được tính là một ký tự chuỗi bình thường, kết quả in ra sẽ bị dư thừa ký tự `$` thành `Player $Alex scored $95 points.`.</t>
+          <t>Tên biến `user-total-count` không hợp lệ vì dấu gạch nối `-` được trình biên dịch/phiên dịch Python hiểu là toán tử trừ chứ không phải ký tự hợp lệ nằm trong tên biến.</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>4</v>
@@ -1057,56 +1061,57 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Trong chương trình Python 3.12, lập trình viên có hai biến lưu thông tin số lượng sản phẩm:
+          <t>Thực thi đoạn mã chuyển đổi kiểu dữ liệu cơ bản sang kiểu luận lý (boolean) trong Python 3.12 dưới đây:
 ```python
-total_item_str = "50"
-bonus_item = 10
+status_a = bool("")
+status_b = bool("False")
+print(status_a, status_b)
 ```
-Để tính tổng số lượng dưới dạng giá trị số nguyên và gán vào biến `total_count` thu được kết quả `60`, câu lệnh chuyển đổi kiểu dữ liệu nào dưới đây là đúng?</t>
+Kết quả hiển thị trên màn hình console là gì và cơ chế chuyển đổi kiểu dữ liệu hoạt động ra sao?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>`total_count = float(total_item_str) + str(bonus_item)`</t>
+          <t>`False True` vì chuỗi rỗng `""` đại diện cho `False`, còn chuỗi chứa văn bản `"False"` có độ dài lớn hơn 0 nên đại diện cho `True`.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai vì hàm `float(total_item_str)` tạo ra kiểu số thực `50.0`, trong khi `str(bonus_item)` tạo ra chuỗi `"10"`. Phép cộng giữa kiểu `float` và kiểu `str` không thể thực hiện được và sẽ dẫn đến lỗi `TypeError: unsupported operand type(s) for +: 'float' and 'str'`.</t>
+          <t>Trong Python, khi chuyển đổi một chuỗi ký tự sang kiểu `bool`, chuỗi rỗng `""` không chứa ký tự nào được tính là `False`. Bất kỳ chuỗi nào chứa ký tự (kể cả chuỗi `"False"` hay chuỗi có khoảng trắng `" "`) đều có độ dài lớn hơn 0 và được đánh giá là `True`.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>`total_count = total_item_str + bonus_item`</t>
+          <t>`True True` vì hàm ép kiểu `bool()` luôn trả về giá trị `True` cho tất cả các đối tượng dữ liệu thuộc kiểu chuỗi ký tự (`str`).</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì biến `total_item_str` mang kiểu chuỗi (`str`), còn `bonus_item` mang kiểu số nguyên (`int`). Trong Python không cho phép cộng trực tiếp chuỗi với số nguyên, chương trình sẽ báo lỗi `TypeError: can only concatenate str (not "int") to str`.</t>
+          <t>Đáp án này sai vì hàm `bool()` đối với chuỗi rỗng `""` sẽ trả về `False`, không phải tất cả chuỗi ký tự đều được quy đổi thành `True`.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>`total_count = int(total_item_str) + bonus_item`</t>
+          <t>`False False` vì cả chuỗi rỗng và chuỗi mang chữ `"False"` đều được cơ chế chuyển đổi kiểu của Python quy về giá trị `False`.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A đúng vì hàm `int(total_item_str)` đã ép thành công chuỗi `"50"` sang kiểu số nguyên `50`, sau đó thực hiện phép cộng số học với số nguyên `bonus_item` (`10`) cho ra kết quả số nguyên `60` chuẩn xác.</t>
+          <t>Đáp án này sai vì giá trị văn bản chữ `"False"` bên trong chuỗi không làm cho hàm `bool()` trả về `False`. Python kiểm tra tính rỗng của tập hợp/chuỗi chứ không phân tích ngữ nghĩa văn bản bên trong.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>`total_count = str(total_item_str) + bonus_item`</t>
+          <t>`True False` vì chuỗi rỗng `""` được tự động quy đổi thành `True`, trong khi chuỗi mang nội dung `"False"` quy đổi thành `False`.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì việc gọi hàm `str(total_item_str)` vẫn giữ nguyên kiểu dữ liệu chuỗi `"50"`. Phép cộng với biến số nguyên `bonus_item` (`10`) tiếp tục gây ra lỗi `TypeError` tương tự như trường hợp không ép kiểu.</t>
+          <t>Đáp án này sai vì cơ chế quy đổi bị ngược; chuỗi rỗng `""` quy đổi ra `False` chứ không phải `True`, và chuỗi `"False"` có độ dài lớn hơn 0 quy đổi ra `True` chứ không phải `False`.</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>4</v>
@@ -1123,51 +1128,57 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Trong dự án Python 3.12, lập trình viên cần khai báo một biến để lưu trữ số lượng sản phẩm tồn kho trong hệ thống (kiểu số nguyên). Theo khuyến nghị về phong cách lập trình chuẩn PEP 8, cách đặt tên biến và gán giá trị nào sau đây là đúng quy chuẩn và hợp lệ?</t>
+          <t>Trong Python 3.12, khi thực hiện chương trình nhập dữ liệu năm sinh của người dùng từ bàn phím để tính tuổi, đoạn mã sau được áp dụng:
+```python
+nam_sinh = input("Nhập năm sinh: ")
+tuoi = 2024 - int(nam_sinh)
+print("Tuổi của bạn là: " + str(tuoi))
+```
+Nếu người dùng nhập vào chuỗi `"2000"`, kết quả hiển thị trên màn hình console là gì và lý do cần thực hiện chuyển đổi kiểu dữ liệu `int(nam_sinh)` là gì?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>`TotalStockCount = 150`</t>
+          <t>Chương trình báo lỗi tại dòng `int(nam_sinh)` vì hàm `int()` không thể thực hiện chuyển đổi một chuỗi thu được từ bàn phím sang dạng số nguyên.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `TotalStockCount = 150` không phù hợp quy chuẩn. Kiểu đặt tên dạng `PascalCase` (viết hoa chữ cái đầu mỗi từ) theo quy định của PEP 8 chỉ được dành riêng cho việc đặt tên Lớp (`Class`), không dùng để đặt tên cho biến thông thường dù cú pháp Python không báo lỗi.</t>
+          <t>Sai vì hàm `int()` hoàn toàn có thể chuyển đổi thành công một chuỗi chứa các chữ số hợp lệ như `"2000"` sang số nguyên `2000`.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>`2024_stock_count = 150`</t>
+          <t>Màn hình hiển thị `Tuổi của bạn là: 20242000`. Phép trừ được tự động chuyển thành thao tác xử lý chuỗi ký tự khi chưa ép kiểu dữ liệu.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `2024_stock_count = 150` vi phạm cú pháp cơ bản của Python. Cú pháp Python quy định tên biến không được phép bắt đầu bằng một chữ số (`2024`). Việc thực thi đoạn mã này sẽ gây ra lỗi cú pháp `SyntaxError: invalid syntax` ngay lập tức.</t>
+          <t>Sai vì phép trừ `-` không hỗ trợ trên kiểu dữ liệu chuỗi (`str`). Nếu không ép kiểu `int(nam_sinh)`, chương trình sẽ báo lỗi `TypeError` chứ không ghép chuỗi.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>`total-stock-count = 150`</t>
+          <t>Màn hình hiển thị `Tuổi của bạn là: 24`. Cần chuyển đổi `int(nam_sinh)` vì hàm `input()` mặc định trả về kiểu chuỗi (`str`), không thể thực hiện phép trừ trực tiếp với số nguyên.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `total-stock-count = 150` vi phạm cú pháp ngôn ngữ. Trong Python, ký tự gạch ngang `-` được thông dịch viên hiểu là toán tử trừ số học. Python sẽ hiểu nhầm đây là biểu thức toán học `total - stock - count` thay vì tên biến, dẫn đến lỗi `SyntaxError` hoặc `NameError` khi khởi tạo.</t>
+          <t>Hàm `input()` trong Python luôn nhận dữ liệu đầu vào dưới dạng chuỗi (`str`). Do đó, để thực hiện phép toán số học `2024 - nam_sinh`, giá trị nhập vào phải được ép kiểu sang số nguyên (`int`). Sau khi tính ra kết quả `24`, hàm `str(tuoi)` chuyển số này lại thành chuỗi để thực hiện nối chuỗi hiển thị ra console.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>`total_stock_count = 150`</t>
+          <t>Màn hình hiển thị `Tuổi của bạn là: 24`. Hàm `input()` tự động nhận diện giá trị nhập vào là số nguyên nên việc sử dụng `int(nam_sinh)` chỉ để đảm bảo chuẩn hóa mã nguồn.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `total_stock_count = 150` là đúng hoàn toàn. Tên biến tuân thủ chuẩn PEP 8 bằng cách sử dụng chữ cái tiếng Anh viết thường, phân cách giữa các từ bằng dấu gạch dưới `_` (`snake_case`), đồng thời khai báo đúng giá trị số nguyên `150` hợp lệ trong Python.</t>
+          <t>Sai vì hàm `input()` trong Python 3.12 không tự động chuyển đổi kiểu dữ liệu mà luôn trả về một chuỗi ký tự (`str`).</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>4</v>
@@ -1184,58 +1195,57 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã lệnh Python 3.12 thực thi việc tính toán tổng chi phí đơn hàng và xuất ra màn hình console như sau:
+          <t>Trong ngôn ngữ lập trình Python 3.12, đoạn mã khởi tạo thông tin cho một học viên như sau:
 ```python
-item_price = 50
-item_quantity = 3
-total_price = item_price * item_quantity
-print("Total cost: " + str(total_price) + "$")
+so_luong_hoc_vien = 30
+diem_trung_binh = 8.5
+da_hoan_thanh = True
 ```
-Kết quả hiển thị chính xác trên màn hình console sau khi chạy chương trình là gì?</t>
+Phân tích nào sau đây đánh giá chính xác về quy tắc đặt tên biến (snake_case) và kiểu dữ liệu cơ sở của các biến trên?</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>`Total cost: 503$`</t>
+          <t>Tên biến tuân thủ đúng chuẩn nhưng kiểu dữ liệu bị sai: `so_luong_hoc_vien` thuộc kiểu `float`, `diem_trung_binh` thuộc kiểu `bool`, và `da_hoan_thanh` thuộc kiểu `int`.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `Total cost: 503$` sai do học viên nhầm lẫn giữa phép toán nhân số học với phép ghép chuỗi. Do cả `item_price` (50) và `item_quantity` (3) đều thuộc kiểu số nguyên `int`, toán tử `*` thực hiện phép nhân số học ($50 \times 3 = 150$) chứ không phải là ghép nối chuỗi ký tự `"50"` và `"3"`.</t>
+          <t>Sai vì kiểu dữ liệu gán cho các biến không đúng với giá trị khởi tạo (`30` là số nguyên `int`, `8.5` là số thực `float`, `True` là kiểu `bool`).</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>`TypeError: can only concatenate str (not "int") to str`</t>
+          <t>Tên biến vi phạm quy tắc đặt tên vì chứa dấu gạch dưới; biến `so_luong_hoc_vien` thuộc kiểu `str`, `diem_trung_binh` thuộc kiểu `int`, và `da_hoan_thanh` thuộc kiểu `str`.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `TypeError: can only concatenate str (not "int") to str` sai. Lỗi này chỉ xuất hiện nếu lập trình viên không sử dụng hàm `str()` để chuyển đổi biến `total_price` (kiểu `int`) sang kiểu `str` trước khi ghép chuỗi. Do trong code đã gọi `str(total_price)` nên chương trình chạy hoàn toàn bình thường.</t>
+          <t>Sai vì quy tắc `snake_case` khuyến khích dùng dấu gạch dưới `_`. Đồng thời các kiểu dữ liệu của biến bị xác định sai hoàn toàn.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>`Total cost: 150$`</t>
+          <t>Tên biến vi phạm quy tắc vì không viết hoa chữ cái đầu tiên; biến `so_luong_hoc_vien` thuộc kiểu `bool`, `diem_trung_binh` thuộc kiểu `str`, và `da_hoan_thanh` thuộc kiểu `float`.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `Total cost: 150$` là đúng. Phép toán `item_price * item_quantity` tính ra giá trị số `150`. Hàm `str(total_price)` chuyển đổi số `150` thành chuỗi `"150"`. Toán tử `+` thực hiện ghép 3 chuỗi `"Total cost: "`, `"150"` và `"$"` lại thành chuỗi hoàn chỉnh `Total cost: 150$`.</t>
+          <t>Sai vì tên biến thông thường trong Python dùng chữ cái viết thường (`snake_case`), không bắt buộc viết hoa chữ cái đầu. Các kiểu dữ liệu nêu trong câu này cũng hoàn toàn sai.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>`Total cost: item_price * item_quantity$`</t>
+          <t>Tên biến tuân thủ đúng chuẩn `snake_case` với chữ cái viết thường phân cách bằng dấu gạch dưới; biến `so_luong_hoc_vien` thuộc kiểu `int`, `diem_trung_binh` thuộc kiểu `float`, và `da_hoan_thanh` thuộc kiểu `bool`.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `Total cost: item_price * item_quantity$` sai do học viên hiểu nhầm rằng Python sẽ in ra tên biểu thức. Trong Python, biểu thức toán học nằm ngoài chuỗi ký tự sẽ được tính toán thành giá trị dữ liệu cụ thể trước khi thực hiện chuyển đổi hoặc ghép chuỗi.</t>
+          <t>Quy tắc đặt tên biến chuẩn trong Python sử dụng chữ cái viết thường và dấu gạch dưới `_` để phân cách các từ (`snake_case`). Giá trị `30` thuộc kiểu số nguyên (`int`), `8.5` thuộc kiểu số thực (`float`), và `True` thuộc kiểu logic (`bool`).</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>4</v>
@@ -1252,58 +1262,57 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 khởi tạo và kiểm tra kiểu dữ liệu của các biến dưới đây:
+          <t>Xét đoạn mã Python 3.12 thực hiện thao tác nhập và xuất thông tin kết quả học tập sau:
 ```python
-user_rating = 4.5
-is_active_session = "True"
-print(type(user_rating))
-print(type(is_active_session))
+ten_hoc_vien = input("Nhập tên: ")
+diem_dau_vao = float(input("Nhập điểm: "))
+print("Học viên", ten_hoc_vien, "có điểm là:", diem_dau_vao)
 ```
-Kết quả hiển thị trên màn hình console của hai dòng lệnh `print` lần lượt là gì?</t>
+Nếu người dùng nhập tên là `"Nguyễn Văn A"` và nhập điểm là `"9"`, kết quả in ra màn hình console và kiểu dữ liệu của biến `diem_dau_vao` là gì?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'int'&gt;` và `&lt;class 'str'&gt;`</t>
+          <t>Chương trình báo lỗi `ValueError` tại dòng 2 vì hàm `float()` không chấp nhận đầu vào là một chuỗi ký tự chữ số.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `&lt;class 'int'&gt;` và `&lt;class 'str'&gt;` sai ở kiểu dữ liệu của biến thứ nhất. Giá trị `4.5` chứa dấu chấm thập phân nên mang kiểu số thực `float`. Kiểu `int` trong Python chỉ đại diện cho các số nguyên không có phần thập phân (ví dụ: `4`).</t>
+          <t>Sai vì hàm `float()` hoàn toàn chấp nhận các chuỗi ký tự chữ số hợp lệ như `"9"` và chuyển đổi thành số thực `9.0` mà không gây ra lỗi.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'float'&gt;` và `&lt;class 'str'&gt;`</t>
+          <t>Màn hình in ra `Học viênNguyễn Văn Acó điểm là:9.0` và biến `diem_dau_vao` vẫn giữ kiểu dữ liệu chuỗi (`str`).</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `&lt;class 'float'&gt;` và `&lt;class 'str'&gt;` là đúng. Giá trị `4.5` chứa phần thập phân nên Python tự động nhận diện thuộc kiểu số thực `float`. Giá trị `"True"` nằm trong cặp dấu ngoặc kép `""` nên được Python coi là một chuỗi văn bản thuộc kiểu `str`, không phải kiểu Boolean.</t>
+          <t>Sai vì hàm `print()` khi nhận nhiều tham số phân cách bởi dấu phẩy sẽ tự động thêm khoảng trắng giữa các phân đoạn, và biến đã được ép kiểu thành `float` chứ không còn là `str`.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'float'&gt;` và `&lt;class 'bool'&gt;`</t>
+          <t>Màn hình in ra `Học viên Nguyễn Văn A có điểm là: 9` và biến `diem_dau_vao` có kiểu dữ liệu số nguyên (`int`).</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `&lt;class 'float'&gt;` và `&lt;class 'bool'&gt;` sai do bẫy nhầm lẫn giữa giá trị Boolean `True` và chuỗi `"True"`. Khi một giá trị được bọc trong cặp dấu ngoặc kép `""`, Python luôn xử lý nó dưới dạng kiểu chuỗi `str`, bất kể nội dung bên trong có trùng với từ khóa Boolean hay không.</t>
+          <t>Sai vì hàm `float()` ép kiểu giá trị nhập vào thành số thực (`9.0`) chứ không phải số nguyên (`9`).</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>`&lt;class 'double'&gt;` và `&lt;class 'bool'&gt;`</t>
+          <t>Màn hình in ra `Học viên Nguyễn Văn A có điểm là: 9.0` và biến `diem_dau_vao` có kiểu dữ liệu số thực (`float`).</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `&lt;class 'double'&gt;` và `&lt;class 'bool'&gt;` sai vì nhầm lẫn với các ngôn ngữ lập trình khác như Java/C++. Ngôn ngữ Python không có kiểu dữ liệu tên là `double`, tất cả các số thực đều thuộc lớp `float`. Đồng thời giá trị `"True"` có dấu ngoặc kép nên phải mang kiểu `str`.</t>
+          <t>Hàm `float()` đã chuyển đổi chuỗi `"9"` thành số thực `9.0`. Khi truyền nhiều đối số cách nhau bằng dấu phẩy trong hàm `print()`, Python sẽ tự động chèn một khoảng trắng giữa các giá trị khi in ra màn hình console.</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>4</v>
@@ -1320,58 +1329,51 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Một lập trình viên viết đoạn mã Python 3.12 sau để tính tổng tiền đơn hàng sau khi cộng thuế từ dữ liệu do người dùng nhập vào console:
-```python
-item_price = input("Enter item price: ")
-tax_amount = 5
-total_price = item_price + tax_amount
-print(total_price)
-```
-Khi nhập vào giá trị `100`, chương trình không thể thực hiện phép cộng và phát sinh lỗi `TypeError: can only concatenate str (not "int") to str` tại dòng 3. Phân tích nguyên nhân và giải pháp khắc phục nào sau đây là chính xác?</t>
+          <t>Khi xây dựng ứng dụng Python đầu tiên để tiếp nhận dữ liệu người dùng từ console, lập trình viên cần khởi tạo biến lưu trữ số lượng sản phẩm nhập vào. Cú pháp nào dưới đây vừa tuân thủ đúng quy tắc đặt tên biến chuẩn (`snake_case`) vừa chuyển đổi chính xác dữ liệu nhập từ bàn phím thành số nguyên?</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Hàm `print()` ở dòng 4 không thể in được biến kiểu số nguyên `total_price` nếu không sử dụng f-string hoặc chuyển thành `str(total_price)`.</t>
+          <t>```product quantity = int(input())```</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì hàm `print()` trong Python có khả năng tự động ép kiểu và hiển thị hầu hết các kiểu dữ liệu cơ sở (bao gồm `int`, `float`, `str`, `bool`) ra màn hình console mà không cần phải chủ động chuyển đổi về `str` hoặc dùng f-string. Lỗi thực tế xảy ra ở dòng 3 do phép cộng không đồng nhất kiểu dữ liệu chứ không phải ở dòng 4.</t>
+          <t>Tên biến `product quantity` vi phạm quy tắc đặt tên do chứa khoảng trắng phân tách giữa các từ, dẫn đến lỗi cú pháp `SyntaxError` trong Python.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Hàm `input()` mặc định trả về dữ liệu kiểu `str`. Phép cộng `+` giữa `str` (`item_price`) và `int` (`tax_amount`) không hợp lệ. Cần ép kiểu chuỗi sang số nguyên: `item_price = int(input("Enter item price: "))`.</t>
+          <t>```1st_product_qty = int(input())```</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A chính xác vì hàm `input()` trong Python luôn trả về một chuỗi ký tự (kiểu `str`), bất kể người dùng nhập vào số hay chữ. Khi thực hiện `item_price + tax_amount`, Python hiểu đây là phép cộng giữa `str` và `int`, điều này vi phạm quy tắc định kiểu nghiêm ngặt (strongly typed) của Python và gây ra lỗi `TypeError`. Giải pháp chuẩn xác là dùng hàm `int()` để chuyển đổi kết quả của `input()` thành số nguyên trước khi tính toán.</t>
+          <t>Tên biến `1st_product_qty` vi phạm quy tắc đặt tên trong Python do bắt đầu bằng chữ số (`1st`), gây ra lỗi cú pháp `SyntaxError` khi thực thi chương trình.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Cú pháp khai báo biến `item_price` bị sai quy tắc PEP 8, bắt buộc phải đổi tên thành `itemPrice` theo chuẩn `camelCase` thì Python mới cho phép tính toán.</t>
+          <t>```product_quantity = int(input())```</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai vì PEP 8 khuyến nghị sử dụng quy tắc đặt tên `snake_case` (như `item_price`) cho các biến trong Python. Việc sử dụng `camelCase` hay `snake_case` chỉ liên quan đến phong cách viết code (style guide) và tính đồng nhất, hoàn toàn không gây ra lỗi cú pháp hay lỗi thực thi `TypeError` ở thời điểm runtime.</t>
+          <t>Cú pháp `int(input())` chuyển đổi chuỗi nhập từ console thành số nguyên. Tên biến `product_quantity` tuân thủ đúng quy tắc `snake_case` (viết chữ thường, phân tách bằng dấu gạch dưới, bắt đầu bằng chữ cái).</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Biến `tax_amount` được gán trực tiếp bằng số `5` nên Python tự động hiểu là kiểu `str`, dẫn đến việc cả hai biến đều là chuỗi nhưng khác loại.</t>
+          <t>```product-quantity = int(input())```</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì trong Python, khi gán giá trị số không có dấu ngoặc kép `tax_amount = 5`, trình thông dịch luôn xác định biến này thuộc kiểu dữ liệu số nguyên (`int`). Python không bao giờ tự động chuyển số nguyên thành kiểu `str` khi khai báo như vậy.</t>
+          <t>Tên biến `product-quantity` vi phạm quy tắc đặt tên vì chứa dấu gạch ngang (`-`), khiến Python hiểu nhầm đây là phép toán trừ giữa hai biến `product` và `quantity`.</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>6</v>
@@ -1388,58 +1390,51 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Trong quá trình khởi tạo các biến lưu trữ thông tin hệ thống bằng Python 3.12, một lập trình viên thực thi đoạn mã sau:
-```python
-user_age = 25
-1st_score = 90
-total_point = user_age + 1st_score
-print(total_point)
-```
-Chương trình ngay lập tức ngưng hoạt động và thông báo lỗi `SyntaxError: invalid syntax` tại vị trí dòng 2 (`1st_score = 90`). Nguyên nhân nào sau đây giải thích chính xác lỗi cú pháp trên?</t>
+          <t>Trong Python 3.12, hàm `input()` luôn trả về giá trị thuộc kiểu chuỗi (`str`). Nếu người dùng nhập giá trị `25` từ bàn phím và chương trình thực thi biểu thức `result = input() + "5"`, biến `result` sẽ nhận giá trị và kiểu dữ liệu nào?</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Số `90` là một giá trị số nguyên nên bắt buộc biến `1st_score` phải được khai báo kèm từ khóa `int` ở phía trước như `int 1st_score = 90`.</t>
+          <t>Giá trị `25.5` và thuộc kiểu dữ liệu số thực (`float`).</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì Python là ngôn ngữ có kiểu dữ liệu động (dynamically typed). Người viết mã không cần và không được khai báo từ khóa kiểu dữ liệu trước tên biến giống như C/C++/Java. Cú pháp `int 1st_score = 90` cũng sẽ gây ra lỗi `SyntaxError` khác.</t>
+          <t>Kết quả `25.5` thuộc kiểu `float` là không chính xác vì toán tử `+` giữa hai chuỗi thực hiện ghép chuỗi chứ không thực hiện phép tính toán số thực.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Do biến `user_age` ở dòng 1 dùng kiểu `snake_case`, nên biến ở dòng 2 không được phép chứa chữ số để tránh xung đột trình biên dịch Python 3.12.</t>
+          <t>Giá trị `255` và thuộc kiểu dữ liệu số nguyên (`int`).</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì Python hoàn toàn cho phép tên biến chứa chữ số ở các vị trí phía sau (ví dụ: `score_1st` hoặc `score1`), miễn là chữ số đó không nằm ở vị trí đầu tiên của tên biến. Quy tắc `snake_case` không cấm chứa chữ số.</t>
+          <t>Kết quả `255` thuộc kiểu `int` là sai vì biểu thức không chứa bất kỳ hàm ép kiểu nào (`int()`), do đó kết quả vẫn giữ nguyên kiểu chuỗi `str`.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Tên biến `1st_score` vi phạm quy tắc đặt tên định danh (identifier) trong Python vì bắt đầu bằng chữ số (`1`). Quy tắc bắt buộc là tên biến phải bắt đầu bằng chữ cái hoặc dấu gạch dưới (`_`).</t>
+          <t>Giá trị `30` và thuộc kiểu dữ liệu số nguyên (`int`).</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A chính xác vì quy tắc định danh (identifier) của Python quy định tên biến chỉ được phép bắt đầu bằng một chữ cái (a-z, A-Z) hoặc dấu gạch dưới (`_`), không được phép bắt đầu bằng chữ số. Đặt tên `1st_score` làm trình thông dịch Python không thể phân biệt giữa một hằng số và một định danh biến, do đó báo lỗi `SyntaxError` ngay bước phân tích cú pháp (parsing).</t>
+          <t>Kết quả `30` thuộc kiểu `int` chỉ thu được khi giá trị từ `input()` được ép kiểu thành số nguyên bằng `int(input())` trước khi thực hiện phép cộng với số `5`.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Từ `1st` là một từ khóa dự thưởng (reserved keyword) của Python 3.12 được dành riêng cho việc truy xuất phần tử đầu tiên.</t>
+          <t>Giá trị `"255"` và thuộc kiểu dữ liệu chuỗi ký tự (`str`).</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai vì `1st` không phải là một từ khóa dự thưởng (reserved keyword) trong Python. Danh sách các từ khóa của Python (như `def`, `class`, `import`,...) hoàn toàn không chứa bất kỳ từ nào bắt đầu bằng ký tự số.</t>
+          <t>Hàm `input()` mặc định trả về chuỗi `"25"`. Toán tử `+` khi thực hiện giữa hai chuỗi ký tự (`"25"` và `"5"`) sẽ thực hiện thao tác nối chuỗi, tạo ra kết quả `"255"` thuộc kiểu `str`.</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>6</v>
@@ -1456,55 +1451,47 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Xem xét đoạn mã Python 3.12 xử lý định dạng chuỗi xuất ra console và kiểm tra kiểu dữ liệu sau đây:
-```python
-student_name = "Alex"
-current_age = 19
-summary_info = f"Student {student_name} will be {current_age + 1} next year."
-print(summary_info)
-print(type(summary_info))
-```
-Khi đoạn mã trên được thực thi, màn hình console sẽ hiển thị kết quả chính xác như thế nào?</t>
+          <t>Một ứng dụng console cần tính tổng chi phí đơn hàng bằng cách nhân đơn giá (nhập từ bàn phím dưới dạng số thực) với số lượng sản phẩm (nhập từ bàn phím dưới dạng số nguyên). Cú pháp Python nào dưới đây thực hiện chuyển đổi kiểu dữ liệu chính xác và trả về kết quả thuộc kiểu số thực (`float`)?</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Dòng thứ nhất hiển thị `Student Alex will be 20 next year.` và dòng thứ hai hiển thị `&lt;class 'str'&gt;`.</t>
+          <t>```total_cost = float(input()) * int(input())```</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Đáp án A chính xác. Trong Python 3.12, tính năng f-string cho phép tính toán trực tiếp biểu thức bên trong cặp ngoặc nhọn `{}`. Biểu thức `{current_age + 1}` được tính toán thành `19 + 1 = 20`. Sau đó, kết quả này được nhúng vào chuỗi và gán cho `summary_info`. Bản chất của biểu thức f-string luôn trả về một đối tượng kiểu chuỗi (`str`), do đó `type(summary_info)` trả về `&lt;class 'str'&gt;`.</t>
+          <t>Hàm `float(input())` chuyển đơn giá thành số thực và `int(input())` chuyển số lượng thành số nguyên. Trong Python, phép nhân giữa kiểu `float` và `int` sẽ tự động thực hiện ép kiểu ngầm định để trả về kết quả thuộc kiểu `float`.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Dòng thứ nhất hiển thị `Student Alex will be 20 next year.` và dòng thứ hai hiển thị `&lt;class 'int'&gt;`.</t>
+          <t>```total_cost = str(input()) * int(input())```</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Đáp án D sai vì mặc dù biểu thức `current_age + 1` cho ra kết quả số nguyên `20`, nhưng giá trị của toàn bộ biểu thức f-string `summary_info` là chuỗi văn bản hoàn chỉnh. Do đó kiểu dữ liệu của `summary_info` phải là `str`, không thể là `int`.</t>
+          <t>Hàm `str(input())` trả về kiểu chuỗi. Phép nhân giữa kiểu `str` và `int` trong Python thực hiện thao tác lặp lại chuỗi chứ không thực hiện phép tính số học.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Dòng thứ nhất hiển thị `Student Alex will be 191 next year.` và dòng thứ hai hiển thị `&lt;class 'str'&gt;`.</t>
+          <t>```total_cost = int(input()) * int(input())```</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Đáp án B sai vì biến `current_age` có kiểu số nguyên (`int` giá trị `19`). Trong biểu thức `{current_age + 1}`, toán tử `+` thực hiện phép cộng số học giữa hai số nguyên (`19 + 1 = 20`), chứ không phải thực hiện phép nối chuỗi (`"19" + "1" = "191"`). Phép nối chuỗi chỉ xảy ra khi hai vế đều là kiểu chuỗi `str`.</t>
+          <t>Biểu thức `int(input()) * int(input())` ép cả hai giá trị về kiểu số nguyên, do đó phép nhân này sẽ trả về kết quả thuộc kiểu `int` chứ không phải kiểu số thực (`float`).</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Chương trình sẽ dừng và báo lỗi `TypeError` vì f-string không hỗ trợ thực hiện biểu thức tính toán số học `{current_age + 1}` bên trong chuỗi.</t>
+          <t>```total_cost = float(input()) + str(input())```</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Đáp án C sai vì f-string trong Python cho phép đưa bất kỳ biểu thức Python hợp lệ nào vào trong cặp ngoặc nhọn `{}` (bao gồm các phép toán số học `+`, `-`, `*`, `/`). Trình thông dịch sẽ thực thi biểu thức đó trước rồi tự động ép kiểu kết quả về chuỗi để nhúng vào chuỗi lớn.</t>
+          <t>Phép cộng `+` giữa kiểu `float` (từ `float(input())`) và kiểu `str` (từ `str(input())`) sẽ phát sinh lỗi `TypeError` do Python không hỗ trợ cộng trực tiếp số với chuỗi.</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -1525,67 +1512,53 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Khi thực hiện rà soát mã nguồn (code review) theo chuẩn thiết kế mã nguồn PEP 8 trong môi trường Python 3.12, một lập trình viên gặp lỗi cú pháp `SyntaxError` do đặt tên biến không hợp lệ. Khối mã nào dưới đây được sửa đổi đúng quy chuẩn `snake_case` của PEP 8 và thực thi thành công không phát sinh lỗi?</t>
+          <t>Khi thực thi đoạn mã Python 3.12 sau đây trên console:
+```python
+a = input()
+b = input()
+print(a + b)
+```
+Nếu người dùng nhập dữ liệu từ bàn phím lần lượt là `10` và `20`, kết quả hiển thị trên màn hình console là gì và tại sao?</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>```python
-OrderTotal = 150.5
-CustomerName = "Minh"
-IsVerifiedUser = True
-FirstOrderDate = "2024-01-01"
-```</t>
+          <t>Kết quả xuất ra là `10 20` vì hàm `print()` sẽ tự động thêm khoảng trắng phân cách vào giữa các giá trị khi thực hiện phép cộng hai biến đầu vào.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai về mặt chuẩn mực thiết kế vì cách đặt tên kiểu `PascalCase` (`OrderTotal`, `CustomerName`) vi phạm hướng dẫn phong cách PEP 8 đối với biến thông thường (vốn dành riêng cho tên lớp - Class), khiến mã nguồn thiếu tính đồng nhất và gây khó khăn trong việc bảo trì dự án Python.</t>
+          <t>Phân tích này sai vì toán tử `+` nối ghép hai chuỗi ký tự liền nhau không chứa khoảng trắng. Việc tự động thêm khoảng trắng phân cách chỉ xảy ra khi truyền nhiều tham số riêng biệt trong hàm `print(a, b)`.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>```python
-order_total = 150.5
-customer_name = "Minh"
-is_verified_user = True
-first_order_date = "2024-01-01"
-```</t>
+          <t>Kết quả xuất ra là `1020` vì hàm `input()` luôn trả về giá trị kiểu chuỗi (`str`), nên toán tử `+` sẽ thực hiện phép nối hai chuỗi ký tự.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì tất cả các biến (`order_total`, `customer_name`, `is_verified_user`, `first_order_date`) được khai báo tuân thủ hoàn toàn quy chuẩn PEP 8 bằng kiểu `snake_case` (chữ cái viết thường, phân cách bằng dấu gạch dưới `_`) và bắt đầu bằng chữ cái hợp lệ, giúp Python 3.12 biên dịch thành công mà không gặp bất kỳ lỗi cú pháp nào.</t>
+          <t>Hàm `input()` trong Python mặc định luôn nhận giá trị nhập vào từ bàn phím dưới dạng chuỗi ký tự (`str`). Khi sử dụng toán tử `+` giữa hai chuỗi ký tự `"10"` và `"20"`, Python sẽ nối hai chuỗi này lại thành `"1020"` chứ không thực hiện phép cộng số học.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>```python
-order-total = 150.5
-customer-name = "Minh"
-is-verified-user = True
-first-order-date = "2024-01-01"
-```</t>
+          <t>Chương trình báo lỗi `TypeError` vì toán tử `+` không được hỗ trợ để làm việc với các giá trị trả về trực tiếp từ hàm `input()`.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì sử dụng dấu gạch ngang (`-`) trong tên biến (`order-total`). Trình thông dịch Python 3.12 sẽ nhận diện dấu gạch ngang là toán tử trừ (`-`), dẫn tới việc hiểu nhầm đây là một phép toán chứ không phải khai báo biến, gây ra lỗi `SyntaxError: cannot assign to expression`.</t>
+          <t>Phân tích này không chính xác vì toán tử `+` hoàn toàn hợp lệ đối với hai chuỗi ký tự, đóng vai trò là toán tử nối chuỗi (concatenation) chứ không gây ra lỗi kiểu dữ liệu.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>```python
-1st_order_total = 150.5
-customer_name = "Minh"
-is_verified_user = True
-first_order_date = "2024-01-01"
-```</t>
+          <t>Kết quả xuất ra là `30` vì Python tự động nhận diện các chuỗi gồm các ký tự số và chuyển chúng về kiểu số nguyên trước khi thực hiện phép cộng.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì tên biến `1st_order_total` bắt đầu bằng ký tự chữ số (`1`). Quy tắc định danh của Python quy định tên biến chỉ được bắt đầu bằng chữ cái hoặc dấu gạch dưới `_`. Việc khai báo này sẽ khiến trình thông dịch Python 3.12 báo lỗi `SyntaxError: invalid syntax` ngay khi khởi tạo.</t>
+          <t>Phân tích này không chính xác vì Python không tự động chuyển đổi kiểu dữ liệu (implicit type conversion) từ `str` sang `int` khi thực hiện toán tử `+`. Lập trình viên phải gọi hàm `int()` thủ công nếu muốn thực hiện phép cộng số học.</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -1606,59 +1579,51 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Trong Python 3.12, đoạn mã khởi tạo và tính toán tổng tiền sau đây gặp sự cố ngắt chương trình khi thực thi:
-```python
-item_price = 50000
-quantity_count = 3
-total_amount = item_price * quantity_count
-summary_text = "Total cost: " + total_amount
-print(summary_text)
-```
-Nguyên nhân gây ra lỗi `TypeError` là gì và cách khắc phục nào sử dụng f-string hoặc chuyển đổi kiểu dữ liệu là đúng nhất?</t>
+          <t>Trong ngôn ngữ lập trình Python 3.12, đoạn mã nào dưới đây thực hiện khai báo tên biến hoàn toàn hợp lệ theo đúng quy tắc đặt tên?</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Do nối trực tiếp chuỗi `str` với số nguyên `int`. Cách khắc phục đúng là dùng f-string: `summary_text = f"Total cost: {total_amount}"`.</t>
+          <t>`1st_user_score = 95` là khai báo hợp lệ vì tên biến có thể bắt đầu bằng chữ số miễn là chứa ký tự gạch dưới để phân tách các thành phần.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì toán tử `+` trong Python không tự động ép kiểu khi thực hiện nối một chuỗi `str` với một số nguyên `int`, gây ra lỗi `TypeError`. Việc sử dụng cú pháp f-string `f"Total cost: {total_amount}"` là giải pháp tối ưu trong Python 3.12 giúp tự động nội suy và định dạng giá trị của `total_amount` thành chuỗi một cách an toàn.</t>
+          <t>Khai báo này sai cú pháp (`SyntaxError`) vì quy tắc đặt tên biến trong Python nghiêm cấm tên biến bắt đầu bằng một chữ số.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Do thiếu phương thức chuyển đổi chuỗi của kiểu số. Cách khắc phục đúng là gọi hàm: `summary_text = "Total cost: " + total_amount.to_string()`.</t>
+          <t>`class = 95` là khai báo hợp lệ vì tất cả các từ trong tiếng Anh đều có thể dùng làm tên biến khi gán với giá trị thuộc kiểu số nguyên.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì đối tượng thuộc kiểu `int` trong Python không sở hữu phương thức `.to_string()`. Việc gọi phương thức không tồn tại này sẽ khiến chương trình dừng lại lập tức với lỗi `AttributeError: 'int' object has no attribute 'to_string'`.</t>
+          <t>Khai báo này sai cú pháp vì `class` là một từ khóa dự thưởng (reserved keyword) của ngôn ngữ Python nên không được phép dùng làm tên biến.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Do cú pháp nối chuỗi thiếu từ khóa ép kiểu trực tiếp. Cách khắc phục đúng là dùng cú pháp: `summary_text = "Total cost: " + (str)total_amount`.</t>
+          <t>`user-score = 95` là khai báo hợp lệ vì dấu gạch nối `-` được cho phép sử dụng để nối các từ trong tên biến giúp tăng độ đọc hiểu.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì cú pháp ép kiểu gán nhãn kiểu C/C++ `(str)total_amount` hoàn toàn không tồn tại trong cú pháp Python. Trình thông dịch Python 3.12 sẽ lập tức báo lỗi cú pháp `SyntaxError: invalid syntax`.</t>
+          <t>Khai báo này sai cú pháp vì dấu gạch nối `-` được trình biên dịch Python hiểu là toán tử trừ số học chứ không phải là ký tự hợp lệ nằm trong tên biến.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Do biến `total_amount` chưa được khởi tạo đúng kiểu. Cách khắc phục đúng là bọc ép kiểu: `summary_text = "Total cost: " + int(total_amount)`.</t>
+          <t>`_user_score_1 = 95` là khai báo hợp lệ vì tên biến có thể bắt đầu bằng dấu gạch dưới `_`, chứa chữ cái, chữ số và không trùng từ khóa.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì biến `total_amount` đã mang giá trị kiểu số nguyên `int` (150000). Việc tiếp tục gọi `int(total_amount)` vẫn trả về kiểu `int`, do đó phép nối toán tử `+` với chuỗi `"Total cost: "` vẫn thất bại và tiếp tục ném ra lỗi `TypeError: can only concatenate str (not "int") to str`.</t>
+          <t>Trong Python, tên biến hợp lệ có thể bắt đầu bằng một chữ cái hoặc dấu gạch dưới `_`, theo sau là các chữ cái, chữ số hoặc dấu gạch dưới. Tên biến `_user_score_1` tuân thủ đầy đủ các quy tắc này.</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>6</v>
@@ -1675,54 +1640,51 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 thực hiện chuyển đổi kiểu dữ liệu cơ bản và kiểm tra dữ liệu sau đây:
+          <t>Cho đoạn mã khởi tạo một biến chứa dữ liệu chuỗi số như sau:
 ```python
-raw_input_data = "42.5"
-processed_number = float(raw_input_data)
-final_result = int(processed_number)
-print(type(final_result))
+data_input = "45.75"
 ```
-Khi thực thi chương trình trên, kết quả hiển thị trên màn hình console là gì và cơ chế chuyển đổi kiểu dữ liệu diễn ra như thế nào?</t>
+Đoạn mã nào dưới đây thực hiện chuyển đổi kiểu dữ liệu của biến `data_input` sang kiểu số thực (`float`) thành công trong Python 3.12?</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `&lt;class 'float'&gt;`. Python tự động giữ kiểu dữ liệu `float` cho biến `final_result` để tránh làm mất mát dữ liệu phần thập phân `0.5` của số nguyên.</t>
+          <t>`result = int(data_input)` vì hàm `int()` sẽ tự động cắt bỏ phần thập phân và chuyển chuỗi `"45.75"` thành giá trị số nguyên `45`.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì Python không tự động duy trì kiểu `float` khi người dùng đã chủ động gọi hàm `int()`. Hàm `int()` cưỡng chế chuyển đổi kiểu dữ liệu thành số nguyên và loại bỏ phần lẻ thập phân, do đó biến `final_result` mang kiểu `int` chứ không phải `float`.</t>
+          <t>Phân tích này không chính xác. Trong Python, hàm `int()` sẽ ném ra lỗi `ValueError` khi truyền vào một chuỗi có chứa dấu chấm thập phân như `"45.75"`, chứ không tự động cắt bỏ phần thập phân.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `&lt;class 'str'&gt;`. Biến `final_result` tự động quay trở lại kiểu chuỗi ban đầu do dữ liệu xuất phát `raw_input_data` vốn được khởi tạo dưới dạng chuỗi.</t>
+          <t>`result = bool(data_input)` vì hàm `bool()` phân tích cú pháp chuỗi ký tự số và trả về số thực tương ứng với giá trị nằm trong chuỗi.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì biến trong Python được định kiểu động dựa trên kết quả trả về của phép toán hoặc hàm khởi tạo gần nhất. Việc ép kiểu qua `int()` đã làm thay đổi hoàn toàn kiểu của dữ liệu từ `str` ban đầu sang `int`, chương trình không giữ lại kiểu dữ liệu gốc của biến ban đầu.</t>
+          <t>Phân tích này sai vì hàm `bool()` thực hiện chuyển đổi sang kiểu dữ liệu luận lý (boolean), trả về `True` nếu chuỗi không rỗng và `False` nếu chuỗi rỗng, chứ không trả về số thực.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `&lt;class 'int'&gt;`. Chuỗi `"42.5"` được ép kiểu thành số thực `42.5`, sau đó hàm `int()` cắt bỏ phần thập phân để chuyển đổi thành số nguyên `42`.</t>
+          <t>`result = float(data_input)` vì hàm `float()` nhận vào một chuỗi biểu diễn số hợp lệ và chuyển đổi chính xác thành giá trị kiểu số thực `45.75`.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì hàm `float("42.5")` chuyển đổi thành công chuỗi chữ số thành số thực `42.5`. Tiếp theo, hàm `int(42.5)` thực hiện ép kiểu số thực sang số nguyên bằng cách cắt bỏ hoàn toàn phần thập phân `.5`, thu được giá trị số nguyên `42`. Kết quả `type(final_result)` do đó trả về `&lt;class 'int'&gt;`.</t>
+          <t>Hàm ép kiểu `float()` trong Python nhận một tham số là chuỗi chứa ký tự số (bao gồm cả dấu chấm thập phân hợp lệ) và chuyển đổi thành công thành số thực kiểu `float`.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `ValueError`. Hàm `int()` không thể tiếp nhận một biến số thực làm tham số truyền vào khi thực hiện chuyển đổi kiểu dữ liệu trong Python 3.12.</t>
+          <t>`result = str(data_input)` vì hàm `str()` phân tích chuỗi số đầu vào và chuyển đổi tự động thành kiểu dữ liệu số thực tương ứng.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai vì hàm `int()` trong Python hoàn toàn chấp nhận tham số là một số thực (`float`). Lỗi `ValueError` chỉ xảy ra khi truyền trực tiếp một chuỗi có chứa dấu chấm thập phân vào hàm `int()` (ví dụ `int("42.5")`), còn trường hợp truyền số thực `int(42.5)` là hoàn toàn hợp lệ.</t>
+          <t>Phân tích này sai vì hàm `str()` được dùng để chuyển đổi các kiểu dữ liệu khác về dạng chuỗi ký tự (`string`), do đó `str("45.75")` vẫn giữ nguyên giá trị kiểu chuỗi.</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -1743,58 +1705,56 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 xử lý dữ liệu nhập vào từ người dùng dưới đây:
+          <t>Xét đoạn mã Python 3.12 thực thi việc nhận dữ liệu từ người dùng và xử lý tính toán như sau:
 ```python
-current_year = 2024
-user_age_text = input("Nhập tuổi của bạn: ")
-birth_year = current_year - int(user_age_text)
-print(f"Năm sinh của bạn là: {birth_year}")
+length = input("Nhập chiều dài: ")
+result = length * 2
 ```
-Khi người dùng chạy chương trình và nhập vào giá trị `"20"` từ console, chương trình sẽ hoạt động như thế nào?</t>
+Nếu người dùng nhập vào từ bàn phím số `5`, giá trị của biến `result` thu được là gì và làm thế nào để tính toán ra kết quả số `10`?</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Chương trình dừng lại và báo lỗi `TypeError` vì không thể thực hiện phép trừ giữa kiểu `int` và kết quả thu được từ hàm `input()`.</t>
+          <t>Biến `result` mang giá trị `None` vì biến `length` chưa được khai báo kiểu dữ liệu cố định trước khi gọi hàm `input()`.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_2` sai vì mặc dù hàm `input()` mặc định trả về kiểu dữ liệu `str`, đoạn mã trên đã chủ động gọi hàm ép kiểu `int(user_age_text)` để chuyển chuỗi thành số nguyên trước khi thực hiện phép trừ, do đó không xảy ra lỗi vi phạm kiểu dữ liệu `TypeError`.</t>
+          <t>Python không yêu cầu khai báo trước kiểu dữ liệu cho biến, và kết quả của phép toán giữa chuỗi và số nguyên luôn trả về chuỗi mới chứ không phải `None`.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Chương trình thực thi thành công, ép kiểu thành công chuỗi `"20"` sang số nguyên `20` và in ra dòng chữ `Năm sinh của bạn là: 2004`.</t>
+          <t>Chương trình dừng và xuất hiện lỗi `TypeError` ngay tại dòng 2 do Python không hỗ trợ toán tử `*` giữa kiểu `str` và kiểu `int`.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_1` đúng vì hàm `input()` thu nhận dữ liệu từ console dưới dạng chuỗi ký tự `str` (chuỗi `"20"`). Hàm `int(user_age_text)` đã chuyển đổi thành công chuỗi `"20"` thành số nguyên `20`. Phép trừ `2024 - 20` cho ra kết quả số nguyên `2004`, sau đó được nhúng vào f-string và xuất ra màn hình console chính xác.</t>
+          <t>Python hỗ trợ toán tử `*` giữa `str` và `int` để nhân bản chuỗi, do đó đoạn mã không phát sinh lỗi `TypeError`.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Chương trình thực thi nhưng in ra chuỗi `Năm sinh của bạn là: 2024 - 20` vì biểu thức trong f-string không tự động tính toán.</t>
+          <t>Biến `result` mang giá trị số nguyên `10` do Python 3.12 tự động nhận diện ký tự số nguyên và ép kiểu khi thực hiện phép nhân.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_4` sai vì các biểu thức hoặc biến nằm bên trong cặp dấu ngoặc nhọn `{}` của f-string trong Python luôn được đánh giá và tính toán để trả về giá trị kết quả trước khi ghép vào chuỗi hoàn chỉnh, chứ không giữ nguyên dạng văn bản thô.</t>
+          <t>Python là ngôn ngữ có cơ chế kiểu dữ liệu động nhưng không tự động ép chuỗi thành số nguyên khi thực hiện phép toán số học với số.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `ValueError` vì hàm `input()` trong Python 3.12 đã tự động nhận diện số nguyên nên việc dùng `int()` bị trùng lặp.</t>
+          <t>Biến `result` mang giá trị chuỗi `"55"` do hàm `input()` luôn trả về kiểu `str`; cần sử dụng `int(input(...))` để ép kiểu sang số nguyên.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_3` sai vì trong tất cả các phiên bản Python (kể cả Python 3.12), hàm `input()` luôn trả về kiểu dữ liệu `str` chứ không tự động chuyển đổi sang số nguyên. Việc sử dụng hàm `int()` là bắt buộc và đúng cú pháp khi muốn thực hiện tính toán số học.</t>
+          <t>Trong Python, hàm `input()` mặc định trả về dữ liệu kiểu chuỗi (`str`). Phép nhân giữa chuỗi `"5"` và số nguyên `2` sẽ thực hiện nhân bản chuỗi 2 lần tạo thành `"55"`. Để tính toán số học tạo ra kết quả `10`, cần thực hiện chuyển đổi kiểu dữ liệu của biến `length` sang kiểu số nguyên bằng hàm `int()`.</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>6</v>
@@ -1811,53 +1771,55 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Trong một chương trình Python 3.12, lập trình viên khai báo danh sách các biến để lưu trữ thông tin như sau:
-```python
-total_students = 45
-1st_place_student = "Alice"
-is_active_status = True
-```
-Khi chạy đoạn mã trên, trình phiên dịch của Python sẽ xử lý dòng khai báo biến `1st_place_student = "Alice"` như thế nào?</t>
+          <t>Một lập trình viên tiến hành khai báo các biến lưu trữ dữ liệu hệ thống trong chương trình Python 3.12. Tên biến nào dưới đây tuân thủ đúng quy tắc đặt tên (identifier) và không gây ra lỗi cú pháp `SyntaxError`?</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Phát sinh lỗi `SyntaxError` vì quy tắc đặt tên biến trong Python tuyệt đối không cho phép tên biến bắt đầu bằng chữ số.</t>
+          <t>```python
+_user_score_2024 = 100
+```</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_1` đúng vì theo quy tắc đặt tên định danh (identifier) của Python và chuẩn PEP 8, tên biến chỉ được bắt đầu bằng chữ cái (a-z, A-Z) hoặc dấu gạch dưới `_`, không được bắt đầu bằng chữ số. Do đó, việc đặt tên biến `1st_place_student` vi phạm cú pháp cơ bản và gây ra lỗi `SyntaxError` ngay ở bước phân tích cú pháp.</t>
+          <t>Tên biến `_user_score_2024` hợp lệ vì quy tắc đặt tên định danh trong Python cho phép bắt đầu bằng dấu gạch dưới `_`, theo sau bởi các ký tự chữ cái, chữ số và dấu gạch dưới.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Phát sinh lỗi `TypeError` vì trình biên dịch hiểu nhầm `1st_place_student` là số nguyên `1` kết hợp với chuỗi ký tự.</t>
+          <t>```python
+2024_user_score = 100
+```</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_4` sai vì Python kiểm tra quy tắc cú pháp tên biến trước khi thực thi chương trình và xác định kiểu dữ liệu. Vì vi phạm ngay từ bước phân tích cú pháp nên chương trình bị ngắt và ném ra `SyntaxError` chứ không phải lỗi kiểu dữ liệu `TypeError`.</t>
+          <t>Tên biến `2024_user_score` không hợp lệ vì quy tắc cú pháp Python không cho phép tên biến bắt đầu bằng một chữ số.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Phát sinh lỗi `NameError` vì tên biến chứa chữ số bắt buộc phải viết hoa toàn bộ theo quy định của chuẩn style guide PEP 8.</t>
+          <t>```python
+user-score-2024 = 100
+```</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_2` sai vì lỗi phát sinh là `SyntaxError` (lỗi cú pháp) chứ không phải `NameError` (lỗi gọi biến chưa được định nghĩa). Ngoài ra, PEP 8 khuyến nghị sử dụng quy tắc `snake_case` (chữ thường phân cách bằng dấu gạch dưới) cho biến, chứ không bắt buộc viết hoa khi tên biến chứa chữ số.</t>
+          <t>Tên biến `user-score-2024` không hợp lệ vì chứa ký tự dấu gạch nối `-`, ký tự này được trình biên dịch hiểu là toán tử trừ trong phép toán số học.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Chương trình vẫn chạy bình thường vì Python 3.12 tự động hỗ trợ chuyển tên biến bắt đầu bằng số về dạng hợp lệ `st_place_student_1`.</t>
+          <t>```python
+user@score = 100
+```</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_3` sai vì Python tuân thủ nghiêm ngặt quy tắc cú pháp và không tự động thay đổi hay sửa lại tên biến của người dùng khi phát hiện vi phạm quy tắc đặt tên.</t>
+          <t>Tên biến `user@score` không hợp lệ vì chứa ký tự đặc biệt `@`, cú pháp Python không cho phép chứa các ký tự đặc biệt ngoại trừ dấu gạch dưới `_` trong tên biến.</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -1878,59 +1840,57 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 thực hiện chuyển đổi kiểu dữ liệu và tính toán đơn giá sản phẩm như sau:
+          <t>Xét đoạn mã Python 3.12 thực hiện xuất dữ liệu ra màn hình console như sau:
 ```python
-item_price_text = "99.5"
-item_quantity_text = "2"
-total_cost = float(item_price_text) * int(item_quantity_text)
-result_message = f"Total: {total_cost} - Type: {type(total_cost).__name__}"
-print(result_message)
+name = "Alex"
+age = 25
+print(name, age, sep=" - ")
 ```
-Kết quả hiển thị chính xác trên màn hình console sau khi thực thi đoạn mã trên là gì?</t>
+Kết quả hiển thị chính xác trên màn hình console khi thực thi đoạn mã trên là gì?</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in ra `Total: 199 - Type: int` vì giá trị `199.0` tự động được Python 3.12 làm tròn và chuyển về số nguyên kiểu `int`.</t>
+          <t>`Alex - 25`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_2` sai vì Python không tự động chuyển kiểu `float` về `int` chỉ vì phần thập phân bằng `0`. Giá trị `199.0` vẫn giữ nguyên bản chất là số thực kiểu `float`.</t>
+          <t>Hàm `print()` trong Python tiếp nhận nhiều đối số và tham số `sep=" - "` quy định ký tự phân cách sẽ được chèn vào giữa các giá trị khi xuất ra console.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Chương trình dừng lại và báo lỗi `TypeError` do Python không cho phép thực hiện phép nhân giữa hai kiểu dữ liệu khác nhau (`float` và `int`).</t>
+          <t>Chương trình báo lỗi `TypeError` do không thể xuất các biến khác kiểu dữ liệu (`str` và `int`) trong cùng một lệnh `print()`.</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_4` sai vì Python hỗ trợ hoàn hảo các phép toán số học giữa kiểu số nguyên `int` và kiểu số thực `float` mà không gây ra lỗi `TypeError`.</t>
+          <t>Hàm `print()` tự động chuyển đổi các đối số truyền vào thành dạng chuỗi đại diện trước khi xuất dữ liệu ra console nên không gây ra lỗi `TypeError`.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in ra `Total: 99.599.5 - Type: str` vì các biến ban đầu mang kiểu chuỗi `str` nên thực hiện phép nhân bản chuỗi.</t>
+          <t>`name - age`</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_3` sai vì hai biến `item_price_text` và `item_quantity_text` đã được chuyển đổi kiểu thành công sang `float` và `int` trước khi thực hiện phép nhân, do đó đây là phép toán số học chứ không phải phép lặp chuỗi.</t>
+          <t>Hàm `print()` sẽ xuất giá trị dữ liệu đang lưu trữ bên trong biến `name` và `age` chứ không xuất tên định danh của biến ra màn hình.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in ra `Total: 199.0 - Type: float` vì phép nhân giữa kiểu `float` và `int` tự động trả về kết quả kiểu `float`.</t>
+          <t>`Alex 25 -`</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Đáp án `answer_1` đúng vì `float("99.5")` trả về `99.5` (kiểu `float`) và `int("2")` trả về `2` (kiểu `int`). Trong Python, phép toán số học giữa một số thực `float` và một số nguyên `int` sẽ tự động ép kiểu ép ngầm (implicit type promotion) về kiểu `float`. Kết quả `99.5 * 2` là `199.0` (kiểu `float`), do đó `type(total_cost).__name__` trả về chuỗi `"float"`.</t>
+          <t>Tham số `sep` xác định ký tự phân cách ở giữa các đối số truyền vào, không phải ký tự kết thúc ở cuối dòng.</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>6</v>
@@ -1947,55 +1907,55 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Trong một buổi rà soát mã nguồn Python 3.12, lập trình viên gặp đoạn mã xử lý dữ liệu tài khoản như sau:
+          <t>Trong một chương trình Python 3.12 xử lý dữ liệu đầu vào từ bàn phím, lập trình viên thực thi đoạn mã sau:
 ```python
-initial_balance_text = "500"
-current_balance = int(initial_balance_text)
-initial_balance_text.replace("500", "1000")
-final_account_balance = current_balance + int(initial_balance_text)
-print(f"Account balance: {final_account_balance}")
+val_a = input()
+val_b = input()
+result = val_a + val_b
+print(result)
+print(type(result))
 ```
-Kết quả hiển thị ra màn hình console và bản chất cơ chế xử lý bộ nhớ của Python ở đây là gì?</t>
+Khi người dùng nhập lần lượt là `15` và `25` từ console, kết quả hiển thị trên màn hình console và kiểu dữ liệu của biến `result` sẽ là gì?</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Account balance: 1000`. Do chuỗi (`str`) là kiểu dữ liệu bất biến (immutable), phương thức `.replace()` không làm thay đổi giá trị của biến `initial_balance_text` ban đầu.</t>
+          <t>Hiển thị giá trị `1525` và kiểu dữ liệu là `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Phương án đúng. Trong Python, kiểu dữ liệu chuỗi (`str`) là bất biến (immutable). Khi gọi `initial_balance_text.replace("500", "1000")`, Python tạo ra một đối tượng chuỗi mới chứa giá trị `"1000"` nhưng không gán lại vào biến `initial_balance_text`. Do đó, biến `initial_balance_text` vẫn giữ nguyên giá trị `"500"`. Khi tính toán: `final_account_balance = 500 + int("500") = 1000`.</t>
+          <t>Hàm `input()` trong Python luôn trả về một chuỗi ký tự (`str`) dù người dùng nhập vào các ký số. Do đó, toán tử `+` giữa hai chuỗi ký tự `val_a` và `val_b` sẽ thực hiện phép nối chuỗi (`"15" + "25"` tạo thành `"1525"`), làm cho biến `result` giữ giá trị chuỗi với kiểu dữ liệu là `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `TypeError` ở dòng 4 do biến `initial_balance_text` bị khóa địa chỉ bộ nhớ sau khi gọi hàm ép kiểu `int()` ở dòng 2.</t>
+          <t>Hiển thị giá trị `1525` và kiểu dữ liệu là `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên hiểu sai về cơ chế quản lý bộ nhớ của Python. Việc gọi `int(initial_balance_text)` chỉ đọc giá trị của chuỗi để tạo ra một đối tượng số nguyên mới (`int`), hoàn toàn không khóa hay làm ảnh hưởng đến biến chuỗi ban đầu.</t>
+          <t>Phân tích này sai về kiểu dữ liệu vì mặc dù chuỗi nối lại có ký tự là `"1525"`, kiểu của biến `result` vẫn là `&lt;class 'str'&gt;` chứ không phải kiểu số nguyên `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Account balance: 1500`. Do phương thức `.replace()` đã thay đổi trực tiếp (in-place) giá trị của biến `initial_balance_text` thành `"1000"`.</t>
+          <t>Hiển thị giá trị `40.0` và kiểu dữ liệu là `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên mắc bẫy tư duy khi cho rằng các phương thức xử lý chuỗi làm thay đổi trực tiếp (in-place) đối tượng ban đầu. Thực tế, vì `str` là kiểu dữ liệu bất biến, mọi phương thức biến đổi chuỗi đều trả về một đối tượng mới và cần phép gán (`=`) để lưu lại.</t>
+          <t>Phân tích này sai vì Python không tự động chuyển đổi chuỗi nhập từ `input()` thành kiểu số thực `float`. Toán tử `+` trên hai chuỗi sẽ thực hiện nối chuỗi chứ không tính toán số học.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Account balance: 2000`. Do hàm `int()` tự động cập nhật liên kết tham chiếu đến giá trị của biến chuỗi ban đầu trong bộ nhớ.</t>
+          <t>Hiển thị giá trị `40` và kiểu dữ liệu là `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên nhầm lẫn về cơ chế tham chiếu biến. Hàm `int()` không tạo ra bất kỳ liên kết đồng bộ tự động nào giữa biến kiểu `int` và biến kiểu `str` ban đầu.</t>
+          <t>Đây là hiểu lầm phổ biến khi cho rằng hàm `input()` tự động nhận diện và ép kiểu các ký số nhập từ bàn phím sang kiểu số nguyên `int`. Trong Python, `input()` luôn trả về giá trị kiểu `str` trừ khi được ép kiểu thủ công bằng `int()`.</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
@@ -2016,60 +1976,59 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Xem xét đoạn mã Python 3.12 xử lý dữ liệu cờ trạng thái (flag) được chuyển đổi từ dữ liệu chuỗi và số nguyên dưới đây:
+          <t>Trong quá trình phát triển ứng dụng Python 3.12 xử lý trạng thái và dữ liệu cơ sở, lập trình viên thực thi đoạn mã kiểm tra chuyển đổi kiểu dữ liệu như sau:
 ```python
-status_flag_text = "False"
-retry_count_val = 0
-is_active_session = bool(status_flag_text)
-is_retry_valid = bool(retry_count_val)
-combined_output = f"{is_active_session}_{is_retry_valid}"
-print(f"Session state: {combined_output}")
+status_a = bool("0")
+status_b = bool("")
+status_c = bool(0)
+status_d = bool(-5)
+print(status_a, status_b, status_c, status_d)
 ```
-Kết quả hiển thị ra màn hình console là gì và nguyên nhân do đâu?</t>
+Kết quả in ra màn hình console của đoạn mã trên là gì?</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Session state: True_True`. Vì hàm `bool()` luôn trả về `True` cho tất cả các biến đã được khởi tạo và chứa giá trị khác `None`.</t>
+          <t>`False False False True`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên hiểu sai quy tắc chuyển đổi Falsy trong Python. Số `0` (hoặc `0.0`) khi đưa vào hàm `bool()` luôn cho kết quả là `False`, chứ không phải mọi biến khác `None` đều là `True`.</t>
+          <t>Đây là nhầm lẫn phổ biến khi cho rằng chuỗi `"0"` biểu diễn số 0 nên sẽ được ép kiểu thành `False`. Thực tế, bất kỳ chuỗi ký tự nào không rỗng trong Python khi ép kiểu qua `bool()` đều trả về `True`.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Session state: False_False`. Vì hàm `bool()` phân tích cú pháp chuỗi `"False"` và tự động chuyển đổi thành giá trị Boolean `False`.</t>
+          <t>`False True True False`</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Đây là bẫy tư duy rất phổ biến. Hàm `bool()` không đọc và phân tích nội dung văn bản bên trong chuỗi. Nó chỉ kiểm tra xem chuỗi đó có rỗng hay không (`len &gt; 0`). Vì `"False"` là chuỗi có 5 ký tự (không rỗng), kết quả bắt buộc phải là `True`.</t>
+          <t>Phân tích này đảo ngược toàn bộ quy tắc ép kiểu boolean của Python. Chuỗi rỗng và số 0 là `False`, trong khi chuỗi phi rỗng và các số khác 0 đều có giá trị boolean là `True`.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Session state: True_False`. Vì `bool("False")` trả về `True` do chuỗi không rỗng, còn `bool(0)` trả về `False` do số `0` là giá trị Falsy trong Python.</t>
+          <t>`True False False False`</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Phương án đúng. Trong Python, mọi chuỗi (`str`) không rỗng (kể cả chuỗi chứa chữ `"False"` hay khoảng trắng `" "`) khi chuyển đổi qua `bool()` đều cho kết quả `True`. Đối với kiểu số nguyên (`int`), giá trị `0` luôn chuyển đổi thành `False`. Do đó `is_active_session` là `True` và `is_retry_valid` là `False`, kết hợp lại ra `True_False`.</t>
+          <t>Phân tích này sai ở giá trị của `status_d` khi cho rằng số âm `-5` sẽ chuyển thành `False`. Trong Python, chỉ có số `0` (hoặc `0.0`) được coi là `False`, tất cả các số khác `0` bất kể âm hay dương đều chuyển thành `True`.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Chương trình gặp lỗi `ValueError` ở dòng 3 do hàm `bool()` không chấp nhận tham số đầu vào là một chuỗi văn bản.</t>
+          <t>`True False False True`</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Hàm `bool()` là hàm ép kiểu dữ liệu cơ sở của Python, chấp nhận mọi kiểu dữ liệu đầu vào (`str`, `int`, `float`, ...) và không bao giờ gây ra lỗi `ValueError` trong trường hợp này.</t>
+          <t>Trong Python, hàm `bool()` chuyển đổi một chuỗi phi rỗng (như `"0"`) thành `True` vì chuỗi đó có chứa ký tự. Chuỗi rỗng `""` và số nguyên `0` đều mang giá trị falsy nên chuyển thành `False`. Các số nguyên khác `0` (bao gồm cả số âm `-5`) đều mang giá trị truthy nên chuyển thành `True`.</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>8</v>
@@ -2086,59 +2045,59 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 thực hiện tính toán số học cơ bản và định dạng dữ liệu đầu ra console như sau:
+          <t>Xét đoạn mã Python 3.12 khởi tạo và gán lại giá trị cho các biến cơ sở dưới đây:
 ```python
-total_items = 10
-group_count = 4
-per_group_ratio = total_items / group_count
-output_info = f"Ratio: {per_group_ratio}"
-print(output_info, type(per_group_ratio).__name__, sep=" - ", end=" [END]\n")
+val_x = 2024
+val_y = val_x
+val_x = "Rikkei Academy"
+print(val_y)
+print(type(val_y))
 ```
-Đoạn mã trên xuất kết quả như thế nào ra màn hình console?</t>
+Kết quả hiển thị trên màn hình console khi thực thi đoạn mã trên là gì?</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Ratio: 2.5 - &lt;class 'float'&gt; [END]` (kèm ký tự xuống dòng). Do hàm `type()` trả về chuỗi biểu diễn lớp đầy đủ bao gồm cả thẻ `&lt;class ...&gt;`.</t>
+          <t>Hiển thị giá trị `2024` và kiểu dữ liệu là `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên nhầm lẫn giữa việc in trực tiếp đối tượng `type(per_group_ratio)` (sẽ ra `&lt;class 'float'&gt;`) và việc truy cập thuộc tính `type(per_group_ratio).__name__` (chỉ lấy chuỗi tên định danh của kiểu là `"float"`).</t>
+          <t>Phân tích này sai về kiểu dữ liệu vì đối tượng `2024` ban đầu là một số nguyên có kiểu dữ liệu là `&lt;class 'int'&gt;`, không bị tự động chuyển thành kiểu chuỗi `&lt;class 'str'&gt;` khi gán biến.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Ratio: 2.5 - float [END]` (kèm ký tự xuống dòng). Do phép chia `/` trong Python luôn trả về kiểu `float`, thuộc tính `__name__` lấy tên kiểu dữ liệu dạng chuỗi, và `sep` phân tách các đối số in.</t>
+          <t>Hiển thị giá trị `Rikkei Academy` và kiểu dữ liệu là `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Phương án đúng. Trong Python, toán tử chia toán học `/` giữa hai số nguyên luôn trả về một số thực (`float`), do đó `10 / 4 = 2.5`. Thuộc tính `__name__` của đối tượng kiểu dữ liệu `type(2.5)` trả về chuỗi tên ngắn gọn `"float"`. Hàm `print()` chèn tham số `sep=" - "` vào giữa hai đối số và nối thêm `end=" [END]\n"` ở cuối câu lệnh.</t>
+          <t>Phân tích này sai vì chuỗi ký tự `"Rikkei Academy"` mang kiểu dữ liệu `&lt;class 'str'&gt;`, đồng thời `val_y` không hề thay đổi giá trị thành chuỗi này sau khi `val_x` được gán lại.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Ratio: 2 - int [END]` (kèm ký tự xuống dòng). Do hai số nguyên chia cho nhau trong Python mặc định sẽ cắt bỏ phần thập phân để giữ kiểu số nguyên `int`.</t>
+          <t>Hiển thị giá trị `2024` và kiểu dữ liệu là `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên bị ảnh hưởng bởi quy tắc của các ngôn ngữ lập trình khác (như C/C++/Java) khi cho rằng phép chia hai số nguyên sẽ cho ra số nguyên. Trong Python, toán tử `/` luôn cho kết quả kiểu `float`. Nếu muốn chia lấy phần nguyên, lập trình viên bắt buộc phải dùng toán tử `//`.</t>
+          <t>Trong Python, biến đóng vai trò là nhãn tham chiếu đến đối tượng trong bộ nhớ. Lệnh `val_y = val_x` làm cho `val_y` tham chiếu đến đối tượng số nguyên `2024`. Khi `val_x` được gán lại thành chuỗi `"Rikkei Academy"`, tham chiếu của `val_x` thay đổi nhưng `val_y` vẫn giữ nguyên tham chiếu tới đối tượng số nguyên `2024` ban đầu mang kiểu `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Màn hình in `Ratio: 2.5 float - [END]` (kèm ký tự xuống dòng). Do tham số `sep=" - "` chỉ được chèn vào vị trí cuối cùng trước tham số `end`.</t>
+          <t>Hiển thị giá trị `Rikkei Academy` và kiểu dữ liệu là `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Phương án sai. Học viên hiểu sai cơ chế hoạt động của tham số `sep` (separator). Trong hàm `print()`, `sep` đóng vai trò là chuỗi phân cách được chèn vào giữa các đối số truyền vào (ở đây là giữa `output_info` và `type(per_group_ratio).__name__`), chứ không phải đặt ở cuối cùng.</t>
+          <t>Đây là nhầm lẫn khi nghĩ rằng `val_y` liên kết trực tiếp với biến `val_x` theo dạng liên kết tên biến động. Trong Python, phép gán `val_y = val_x` là gán tham chiếu đến giá trị đối tượng tại thời điểm đó chứ không liên kết hai biến với nhau.</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>8</v>
@@ -2155,58 +2114,58 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Một lập trình viên viết đoạn mã Python 3.12 để tính tổng chi phí đơn hàng và hiển thị kết quả ra console:
+          <t>Khi xây dựng ứng dụng xử lý dữ liệu bằng Python 3.12, một lập trình viên thực hiện khởi tạo và chuyển đổi kiểu dữ liệu như sau:
 ```python
-ItemPrice = "500"
-tax_rate = 0.1
-total_cost = ItemPrice + (ItemPrice * tax_rate)
-print(f"Total: {total_cost}")
+quantity_input = "10"
+unit_price_input = "15.5"
+total = int(quantity_input) * float(unit_price_input)
+print(type(total))
 ```
-Khi khởi tạo và thực thi chương trình, Python 3.12 báo lỗi `TypeError`. Hãy xác định nguyên nhân gây lỗi và giải pháp tối ưu nhất để sửa đoạn mã trên theo đúng quy tắc đặt tên PEP 8 và chuyển đổi kiểu dữ liệu cơ sở.</t>
+Kết quả hiển thị trên màn hình console và bản chất xử lý kiểu dữ liệu của biến `total` là gì?</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Đổi tên biến `ItemPrice` thành `item_price` theo chuẩn `snake_case` của PEP 8; đồng thời ép kiểu `float(item_price)` trước khi thực hiện phép tính nhân và cộng để tránh lỗi `TypeError` do cố gắng nhân chuỗi `str` với số thực `float`.</t>
+          <t>Chương trình phát sinh lỗi `TypeError` vì Python 3.12 không cho phép thực hiện phép nhân trực tiếp giữa số nguyên và số thực.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này hoàn toàn chính xác. Trong Python, toán tử `*` không hỗ trợ nhân một chuỗi `str` (`"500"`) với một số thực `float` (`0.1`), dẫn đến lỗi `TypeError: can't multiply sequence by non-int of type 'float'`. Việc chuyển đổi `item_price = float(item_price)` hoặc dùng `float(item_price)` khi tính toán giúp đưa về cùng kiểu dữ liệu số để tính toán chính xác. Đồng thời, việc đổi `ItemPrice` (PascalCase) thành `item_price` (snake_case) giúp tuân thủ hoàn toàn quy tắc đặt tên biến PEP 8.</t>
+          <t>Phương án này sai vì Python hỗ trợ đầy đủ các phép toán số học giữa kiểu `int` và `float` mà không gây ra lỗi kiểu dữ liệu `TypeError`.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Đổi tên biến `tax_rate` thành `TAX_RATE` và thực hiện khai báo kiểu dữ liệu cố định cho biến theo cú pháp `int ItemPrice = 500` tương tự như ngôn ngữ C/Java.</t>
+          <t>Màn hình in `&lt;class 'float'&gt;` với giá trị `155.0` do phép nhân giữa kiểu `int` và `float` tự động chuyển đổi kết quả về kiểu `float`.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai cú pháp trầm trọng. Python là ngôn ngữ định kiểu động (dynamically typed), không sử dụng cú pháp khai báo kiểu dữ liệu đứng trước tên biến như `int ItemPrice = 500`. Cú pháp này sẽ gây ra lỗi `SyntaxError` ngay khi chạy chương trình.</t>
+          <t>Khi thực hiện phép toán số học giữa một số nguyên kiểu `int` (10) và một số thực kiểu `float` (15.5), Python 3.12 tự động ép kiểu dữ liệu của kết quả lên kiểu `float` nhằm bảo toàn độ chính xác của phần thập phân, do đó `type(total)` trả về `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Giữ nguyên tên biến `ItemPrice` và ép kiểu biến `tax_rate` thành chuỗi `str(tax_rate)` để thực hiện phép cộng chuỗi trực tiếp mà không cần dùng đến toán tử số học.</t>
+          <t>Màn hình in `&lt;class 'int'&gt;` với giá trị `155` do kiểu số nguyên `int` chiếm ưu thế khi thực hiện ép kiểu từ chuỗi dữ liệu ban đầu.</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai về mặt tư duy logic toán học và bẫy cú pháp. Việc chuyển `tax_rate` thành chuỗi `"0.1"` rồi nhân hoặc cộng với `ItemPrice` không giải quyết được bài toán tính tổng chi phí tài chính (giá tiền + thuế), mà sẽ dẫn đến lỗi cú pháp/logic khi nối chuỗi, tạo ra kết quả sai hoàn toàn so với yêu cầu bài toán.</t>
+          <t>Phương án này sai vì Python không ưu tiên kiểu `int` khi thực hiện phép tính số học hỗn hợp; nếu có ít nhất một toán hạng kiểu `float`, kết quả sẽ luôn mang kiểu `float`.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Sử dụng hàm `eval(ItemPrice)` để tự động chuyển đổi kiểu dữ liệu và đổi tên biến `total_cost` thành `TotalCost` để tuân thủ quy tắc PEP 8 cho biến cục bộ.</t>
+          <t>Màn hình in `&lt;class 'str'&gt;` với giá trị `"155.0"` do hai biến ban đầu đều được khởi tạo từ dạng chuỗi ký tự console.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai cả về bảo mật lẫn quy tắc PEP 8. Việc sử dụng `eval()` để chuyển đổi kiểu dữ liệu cơ bản là một thực hành xấu (anti-pattern) gây rủi ro bảo mật nghiêm trọng. Ngoài ra, PEP 8 quy định biến cục bộ phải sử dụng dạng `snake_case` (`total_cost`), việc đổi thành `TotalCost` (PascalCase) là sai quy chuẩn đặt tên biến.</t>
+          <t>Phương án này sai vì các biến `quantity_input` và `unit_price_input` đã được ép kiểu thành công sang `int` và `float` trước khi thực hiện phép nhân, kết quả thu được là một giá trị số chứ không phải chuỗi.</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>8</v>
@@ -2223,53 +2182,54 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Trong một chương trình Python 3.12, lập trình viên viết đoạn mã tính toán và in ra console như sau:
+          <t>Xét đoạn mã Python 3.12 khởi tạo biến và thực hiện phép toán số học như sau:
 ```python
-raw_val = "100"
-multiplier = 2.5
-print(f"Calculated result: {float(raw_val) * multiplier}")
+data_payload = "100"
+data_payload = int(data_payload)
+data_payload = data_payload / 2
+print(type(data_payload))
 ```
-Lập trình viên muốn tái cấu trúc (refactor) đoạn mã để tối ưu khả năng đọc, tuân thủ PEP 8 và giúp công cụ Traceback của Python 3.12 định vị chính xác dòng mã gặp lỗi nếu `raw_val` chứa giá trị không thể chuyển đổi. Cách tái cấu trúc nào sau đây là chuẩn xác nhất?</t>
+Kiểu dữ liệu của biến `data_payload` thu được tại màn hình console là gì và cơ chế xử lý tương ứng của Python là gì?</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Thực hiện ép kiểu gộp trực tiếp hai biến bên trong f-string bằng cú pháp `f"Calculated result: {float(raw_val + multiplier)}"` để giảm số lượng biến cần khởi tạo trong bộ nhớ.</t>
+          <t>Trả về `&lt;class 'int'&gt;` vì giá trị `100` chia hết cho `2` nên Python tự động tối ưu hóa kết quả về dạng số nguyên để tiết kiệm bộ nhớ.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai cú pháp trầm trọng. Cố gắng cộng chuỗi `raw_val` (`"100"`) với số thực `multiplier` (`2.5`) bên trong hàm `float()` sẽ gây lỗi `TypeError: can only concatenate str (not "float") to str` trước khi hàm `float()` kịp xử lý.</t>
+          <t>Phương án này sai vì toán tử `/` trong Python luôn sinh ra kết quả kiểu `float`. Nếu muốn thu được kiểu `int` cho phép chia hết, lập trình viên phải dùng toán tử chia lấy phần nguyên `//`.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Đổi tên biến `raw_val` thành `RawVal` theo dạng PascalCase và thực hiện phép nhân chuỗi `print("Calculated result: " + raw_val * multiplier)` để tránh phải dùng hàm `float()`.</t>
+          <t>Chương trình phát sinh lỗi `TypeError` do không thể gán lại một giá trị kiểu số cho biến đã mang kiểu chuỗi ký tự.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai về mặt cú pháp và quy chuẩn. Phép nhân chuỗi với số thực `raw_val * multiplier` (chuỗi `str` * `float`) sẽ gây ra lỗi `TypeError`. Thêm vào đó, đặt tên biến PascalCase `RawVal` vi phạm quy tắc `snake_case` của PEP 8 dành cho biến thông thường.</t>
+          <t>Phương án này sai vì việc gán lại giá trị khác kiểu cho cùng một biến là hoàn toàn hợp lệ trong Python mà không gây ra bất kỳ lỗi runtime nào.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Tách việc ép kiểu ra dòng riêng `base_val = float(raw_val)`, tính toán `total_val = base_val * multiplier` trước, sau đó mới truyền `total_val` vào `print(f"Calculated result: {total_val}")`.</t>
+          <t>Trả về `&lt;class 'float'&gt;` vì phép chia toán tử `/` trong Python 3.12 luôn trả về kết quả số thực dù phép chia có hết hay không.</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này hoàn toàn chính xác. Việc viết biểu thức chuyển đổi kiểu và tính toán phức tạp trực tiếp bên trong f-string khiến đoạn mã khó đọc và khi xảy ra lỗi `ValueError` (ví dụ `raw_val = "abc"`), Traceback chỉ chỉ ra dòng `print`. Khi tách thành các bước rõ ràng với biến đặt tên `snake_case` chuẩn PEP 8 (`base_val`, `total_val`), trình gỡ lỗi (debugger) và Traceback của Python 3.12 sẽ chỉ định chính xác dòng bị lỗi ép kiểu, giúp nâng cao khả năng bảo trì và tối ưu mã nguồn.</t>
+          <t>Trong Python 3.12, toán tử chia `/` (true division) luôn trả về một giá trị kiểu `float` (kể cả 100 / 2 = 50.0). Đồng thời, Python là ngôn ngữ có cơ chế định kiểu động (dynamic typing), cho phép một biến thay đổi kiểu dữ liệu liên tục qua các phép gán.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Bọc toàn bộ biểu thức vào hàm `exec()` bên trong f-string như `print(f"Calculated result: {exec('float(raw_val) * multiplier')}")` để tăng tốc độ biên dịch của Python 3.12.</t>
+          <t>Trả về `&lt;class 'str'&gt;` vì biến `data_payload` đã được định kiểu cố định là chuỗi ký tự ngay từ thời điểm khởi tạo ban đầu.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai hoàn toàn. Hàm `exec()` được dùng để thực thi chuỗi mã Python động và luôn trả về `None`. Khi đưa vào f-string, kết quả in ra sẽ là `Calculated result: None`, đồng thời làm giảm hiệu năng và gây nguy cơ mất an toàn mã nguồn.</t>
+          <t>Phương án này sai vì Python là ngôn ngữ định kiểu động chứ không phải định kiểu tĩnh (static typing); kiểu của biến được quyết định bởi giá trị hiện tại mà nó trỏ tới chứ không bị cố định từ ban đầu.</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
@@ -2290,54 +2250,55 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 thực thi các thao tác biến và xuất dữ liệu ra console dưới đây:
+          <t>Một kịch bản xử lý dữ liệu console trong Python 3.12 thực hiện các phép gán và xuất dữ liệu như sau:
 ```python
-user_score_str = "85"
-bonus_score = 15
-user_score_str = int(user_score_str) + bonus_score
-print(f"Final score: {user_score_str}")
+x = "50"
+y = "20"
+result_1 = x + y
+result_2 = int(x) + int(y)
+print(result_1, result_2)
 ```
-Xét về mặt thiết kế mã nguồn, tính nhất quán của kiểu dữ liệu (type consistency) và quy chuẩn PEP 8, đoạn mã trên gặp phải vấn đề gì và cách khắc phục tối ưu nhất là gì?</t>
+Kết quả hiển thị chính xác trên màn hình console khi thực thi kịch bản trên là gì?</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Đổi tên biến `user_score_str` thành `UserScoreStr` theo quy chuẩn PascalCase và bắt buộc phải bọc hàm `str()` ngoài cùng như `str(int(user_score_str) + bonus_score)` thì lệnh `print` mới hoạt động.</t>
+          <t>Chương trình phát sinh lỗi `SyntaxError` do hàm `print()` không cho phép truyền vào nhiều biến phân tách bằng dấu phẩy.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai. Thứ nhất, f-string trong Python tự động chuyển đổi các biểu thức bên trong nó thành chuỗi khi xuất ra console, không bắt buộc phải gọi hàm `str()`. Thứ hai, việc đổi tên thành `UserScoreStr` (PascalCase) vi phạm quy tắc `snake_case` của PEP 8 đối với biến.</t>
+          <t>Phương án này sai vì hàm `print()` hỗ trợ nhận nhiều tham số phân cách nhau bằng dấu phẩy `,` và sẽ tự động in các giá trị này ra console trên cùng một dòng, ngăn cách bởi khoảng trắng.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Đoạn mã gây rò rỉ bộ nhớ (memory leak) vì trong Python 3.12, việc gán lại giá trị mới cho biến mà không sử dụng từ khóa `rebind` sẽ tạo ra các vùng nhớ rác không thể giải phóng.</t>
+          <t>Màn hình in ra `5020 5020` do hàm `int()` chỉ có tác dụng kiểm tra định dạng chứ không làm biến đổi kiểu dữ liệu của biến.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai. Python không có từ khóa `rebind`. Hệ thống quản lý bộ nhớ tự động của Python (Garbage Collector) sẽ tự động thu hồi bộ nhớ của giá trị cũ khi số lượng tham chiếu (reference count) của nó giảm về 0, do đó không gây ra rò rỉ bộ nhớ.</t>
+          <t>Phương án này sai vì hàm `int(x)` trả về giá trị kiểu số nguyên được chuyển đổi từ chuỗi `x`, giúp phép cộng ở `result_2` tính toán ra giá trị số `70`.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Đoạn mã sẽ phát sinh lỗi `TypeError` khi thực thi vì Python 3.12 không cho phép gán giá trị kiểu số nguyên `int` vào biến đã được khởi tạo mang kiểu chuỗi `str` trước đó.</t>
+          <t>Màn hình in ra `70 70` do Python 3.12 tự động nhận diện chuỗi ký tự chứa chữ số và chuyển thành số nguyên khi dùng toán tử `+`.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này sai về cơ chế hoạt động của Python. Python là ngôn ngữ định kiểu động (dynamically typed), việc gán lại một giá trị thuộc kiểu dữ liệu khác cho một biến sẵn có là hoàn toàn hợp lệ về mặt cú pháp và không gây ra lỗi `TypeError` ở runtime.</t>
+          <t>Phương án này sai vì Python là ngôn ngữ định kiểu mạnh (strongly typed), không tự động chuyển đổi chuỗi ký tự thành số nguyên trong phép cộng nếu không gọi hàm ép kiểu `int()` một cách rõ ràng.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Biến `user_score_str` bị gán lại (rebind) một giá trị thuộc kiểu `int`, gây bất nhất giữa tên biến (có hậu tố `_str`) và kiểu dữ liệu thực tế; giải pháp là khởi tạo biến mới `total_score = int(user_score_str) + bonus_score`.</t>
+          <t>Màn hình in ra `5020 70` do toán tử `+` thực hiện ghép hai chuỗi ở `result_1` và cộng hai giá trị số nguyên ở `result_2`.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Đáp án này hoàn toàn chính xác. Mặc dù Python cho phép gán lại biến với kiểu dữ liệu khác (dynamic typing), việc gán một giá trị kiểu `int` cho một biến có tên chứa `_str` gây hiểu lầm nghiêm trọng cho người đọc mã nguồn và các công cụ kiểm tra mã tĩnh (linter). Theo nguyên tắc mã sạch (Clean Code) và PEP 8, nên khởi tạo một biến mới có tên thể hiện đúng bản chất dữ liệu như `total_score` thuộc kiểu `int`.</t>
+          <t>Đối với kiểu chuỗi ký tự (`str`), toán tử `+` đóng vai trò là phép nối chuỗi (cho ra `"5020"`). Đối với kiểu số nguyên (`int`), toán tử `+` thực hiện phép cộng đại số (cho ra `70`). Hàm `print()` mặc định phân tách các tham số bằng một khoảng trắng.</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -2358,55 +2319,53 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Một lập trình viên Python viết chương trình xử lý điểm số người dùng nhập từ console như sau:
+          <t>Khi thực hiện đoạn mã Python 3.12 tiếp nhận dữ liệu từ console với giá trị người dùng nhập vào là `"150.75"`:
 ```python
-user_score_input = input("Enter score: ")
-str = "Final score: "
-total_score = float(user_score_input) + 5.5
-output_message = str + str(total_score)
-print(output_message)
+user_input = input()
+price = float(user_input)
+print(type(price))
 ```
-Khi chạy chương trình và nhập `10`, chương trình gặp lỗi `TypeError: 'str' object is not callable` tại dòng thứ 4. Nguyên nhân cốt lõi gây ra lỗi này và cách sửa tối ưu chuẩn PEP 8 là gì?</t>
+Kết quả hiển thị trên màn hình console là gì?</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Nguyên nhân do Python 3.12 không cho phép nối chuỗi bằng toán tử `+`. Cách sửa là chuyển sang dùng `output_message = str.concat(str(total_score))`.</t>
+          <t>Mã nguồn xuất ra màn hình `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Sai. Python 3.12 vẫn cho phép sử dụng toán tử `+` để nối hai chuỗi ký tự. Phương thức `.concat()` không tồn tại trên đối tượng `str` trong Python.</t>
+          <t>Giá trị trả về của `input()` ban đầu là `str`, nhưng biến `price` đã trải qua quá trình chuyển đổi kiểu dữ liệu ép buộc bằng `float()`, do đó kiểu dữ liệu không còn là `str`.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Nguyên nhân do hàm `input()` trả về kiểu dữ liệu `int` nên không thể ép kiểu sang `float` ở dòng 3. Cách sửa là dùng `int(user_score_input)`.</t>
+          <t>Mã nguồn xuất ra màn hình `&lt;class 'bool'&gt;`.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Sai. Hàm `input()` luôn trả về kiểu dữ liệu `str` (chuỗi), và `float("10")` hoàn toàn hợp lệ để chuyển chuỗi thành số thực `10.0`. Lỗi phát sinh không nằm ở dòng 3.</t>
+          <t>Hàm `float()` thực hiện phép chuyển đổi chuỗi số thành kiểu số thực, không chuyển đổi thành kiểu luận lý `bool` trong trường hợp này.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Nguyên nhân do biến `str` đã ghi đè (shadowing) hàm khởi tạo kiểu dữ liệu `str()` tích hợp của Python. Cách sửa là đổi tên biến `str` thành tên khác theo chuẩn PEP 8 (ví dụ: `prefix_message`).</t>
+          <t>Mã nguồn xuất ra màn hình `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Trong Python, tên các kiểu dữ liệu cơ sở như `str`, `int`, `float` là các hàm tích hợp (built-in functions). Việc đặt tên biến trùng tên với `str` làm mất khả năng gọi hàm `str(total_score)`, dẫn đến lỗi `TypeError: 'str' object is not callable`. Quy tắc PEP 8 nghiêm cấm việc dùng tên của built-in làm tên biến.</t>
+          <t>Hàm `input()` mặc định trả về dữ liệu kiểu chuỗi ký tự `str` (ở đây là `"150.75"`). Khi sử dụng `float(user_input)`, giá trị chuỗi này được chuyển đổi thành số thực `150.75`. Do đó, `type(price)` trả về kiểu `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Nguyên nhân do biến `total_score` thuộc kiểu `float` nên không được phép đứng trong câu lệnh `print()`. Cách sửa là gán `total_score = int(total_score)`.</t>
+          <t>Mã nguồn xuất ra màn hình `&lt;class 'int'&gt;`.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Sai. Hàm `print()` có thể in trực tiếp mọi kiểu dữ liệu cơ bản bao gồm `float`. Lỗi xảy ra do việc gọi hàm `str()` ở dòng 4 bị thất bại do biến `str` trước đó đã đè tên hàm built-in.</t>
+          <t>Chuỗi `"150.75"` chứa dấu chấm thập phân nên hàm `float()` chuyển đổi thành số thực chứ không phải số nguyên `int`.</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -2427,59 +2386,51 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Xem xét đoạn mã Python 3.12 xử lý dữ liệu đầu vào từ người dùng dưới đây:
-```python
-raw_price_str = " 199.99 "
-cleaned_price_str = raw_price_str.strip()
-converted_price = int(cleaned_price_str)
-final_price = converted_price * 2
-print(f"Final price: {final_price}")
-```
-Chương trình trên bị dừng đột ngột và báo lỗi `ValueError: invalid literal for int() with base 10: '199.99'` tại dòng 3. Phân tích nguyên nhân và giải pháp xử lý tối ưu nhất là gì?</t>
+          <t>Trong Python 3.12, khi khai báo biến để lưu trữ giá trị cho chương trình, câu lệnh khai báo nào dưới đây vi phạm quy tắc đặt tên định danh (identifier rules) và gây ra lỗi `SyntaxError`?</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Do Python 3.12 đã loại bỏ việc ép kiểu ngầm định và bắt buộc phải khai báo kiểu dữ liệu cho biến `converted_price: int`.</t>
+          <t>`USER_SCORE_2ND = 95`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Sai. Python 3.12 vẫn là ngôn ngữ định kiểu động (dynamically typed) và không bắt buộc khai báo type hint để code có thể thực thi. Type hint trong Python chỉ có tác dụng hỗ trợ kiểm tra tĩnh (static analysis), không thay đổi cơ chế ép kiểu runtime.</t>
+          <t>Tên biến `USER_SCORE_2ND` hợp lệ theo cú pháp Python và thường được sử dụng theo quy ước đặt tên hằng số của PEP 8.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Hàm `int()` không hỗ trợ chuyển đổi trực tiếp chuỗi ký tự chứa dấu chấm thập phân (`"199.99"`) sang số nguyên. Cần chuyển đổi chuỗi sang `float` trước bằng `float(cleaned_price_str)`, sau đó mới ép kiểu sang `int` nếu cần.</t>
+          <t>`_user_score_2 = 95`</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Trong Python, hàm `int()` chỉ có thể ép trực tiếp một chuỗi đại diện cho số nguyên (ví dụ: `"199"`). Khi chuỗi chứa dấu chấm thập phân như `"199.99"`, hàm `int()` sẽ ném lỗi `ValueError`. Giải pháp đúng là dùng `float(cleaned_price_str)` để chuyển chuỗi thành số thực `199.99` trước.</t>
+          <t>Tên biến `_user_score_2` hoàn toàn hợp lệ vì tên biến trong Python có thể bắt đầu bằng dấu gạch dưới `_`.</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Lỗi xuất hiện do phương thức `.strip()` trả về một kiểu dữ liệu không phải chuỗi, làm cho hàm `int()` không nhận diện được giá trị đầu vào.</t>
+          <t>`2nd_user_score = 95`</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Sai. Phương thức `strip()` của chuỗi luôn trả về một đối tượng kiểu `str` mới đã được loại bỏ khoảng trắng hai đầu. Chuỗi trả về ở đây vẫn là `"199.99"`.</t>
+          <t>Theo quy tắc đặt tên biến trong Python, tên định danh tuyệt đối không được phép bắt đầu bằng chữ số. Việc khai báo `2nd_user_score` bắt đầu bằng ký tự `2` khiến trình thông dịch phát sinh lỗi `SyntaxError` ngay khi phân tích cú pháp.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Lỗi do hàm `print()` ở dòng 5 sử dụng f-string không hợp lệ vì chứa phép toán nhân ở dòng trước.</t>
+          <t>`user_score_2nd = 95`</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Sai. Phép nhân `converted_price * 2` thực hiện ở dòng 4 hoàn toàn độc lập với f-string ở dòng 5. Lỗi thực tế đã xảy ra ở dòng 3 nên chương trình bị dừng trước khi chạy tới dòng 5.</t>
+          <t>Tên biến `user_score_2nd` hợp lệ vì chữ số `2` nằm ở giữa tên biến, không vi phạm quy tắc cấm chữ số đứng đầu.</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>8</v>
@@ -2496,59 +2447,57 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 thực hiện tính toán chi phí và in ra kiểu dữ liệu như sau:
+          <t>Khi thực hiện đoạn mã Python 3.12 điều khiển xuất dữ liệu ra màn hình console dưới đây:
 ```python
-input_quantity_str = "10"
-unit_price = 15.0
-total_cost = int(input_quantity_str) * unit_price
-cost_type_name = type(total_cost).__name__
-print(f"Cost: {total_cost}, Type: {cost_type_name}")
+app_name = "Rikkei"
+app_version = "3.12"
+print(app_name, app_version, sep=":", end="!")
 ```
-Kết quả in ra màn hình console của chương trình trên là gì và cơ chế ép kiểu tự động (implicit type coercion) của Python hoạt động như thế nào trong trường hợp này?</t>
+Kết quả nào sau đây hiển thị đúng trên màn hình console?</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Kết quả in ra là `Cost: 150, Type: int` vì phép nhân `10 * 15.0` ra số tròn nên Python tự động tối ưu ép về kiểu `int`.</t>
+          <t>Chuỗi ký tự `Rikkei:3.12!` được xuất ra màn hình console.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Sai. Python không tự động làm tròn hay chuyển `float` thành `int` dựa vào giá trị số phần thập phân bằng 0. Phép toán số học giữa `int` và `float` luôn luôn tạo ra kiểu `float`.</t>
+          <t>Trong hàm `print()`, tham số `sep=":"` thay thế khoảng trắng mặc định phân cách giữa hai đối số `app_name` và `app_version` bằng dấu `:`. Tham số `end="!"` thay thế ký tự xuống dòng mặc định `\n` ở cuối bằng ký tự `!`. Do đó kết quả thu được là `Rikkei:3.12!`.</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `TypeError` ở dòng 3 vì Python không cho phép nhân trực tiếp kiểu `int` với kiểu `float`.</t>
+          <t>Chuỗi ký tự `Rikkei 3.12!` được xuất ra màn hình console.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Sai. Python hỗ trợ hoàn toàn các phép toán số học (+, -, *, /) giữa các kiểu dữ liệu số cơ sở (`int` và `float`) nhờ vào cơ chế ép kiểu tự động (implicit type coercion).</t>
+          <t>Đáp án này sai vì đã bỏ qua tác dụng của tham số `sep=":"`, sử dụng khoảng trắng phân cách mặc định thay vì dấu `:`.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Kết quả in ra là `Cost: 150.0, Type: float`. Trong Python, khi thực hiện phép tính nhân giữa một số nguyên (`int`) và một số thực (`float`), kết quả sẽ tự động được chuyển đổi (coerced) sang kiểu `float` để đảm bảo độ chính xác.</t>
+          <t>Chuỗi ký tự `Rikkei:3.12` được xuất ra màn hình console.</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Khi nhân `int` (10) với `float` (15.0), Python tự động thúc đẩy (promote) số nguyên lên số thực để thực hiện phép tính. Kết quả thu được luôn là một số thực thuộc kiểu `float` (`150.0`), do đó `type(total_cost).__name__` trả về chuỗi `"float"`.</t>
+          <t>Đáp án này sai vì đã bỏ qua tác dụng của tham số `end="!"`, làm mất ký tự `!` ở cuối kết quả xuất.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Kết quả in ra là `Cost: 150.0, Type: str` vì kết quả được đặt bên trong f-string nên biến `total_cost` bị chuyển kiểu thành `str`.</t>
+          <t>Chuỗi ký tự `Rikkei 3.12:` được xuất ra màn hình console.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Sai. Phép tính và việc lấy `type(total_cost)` diễn ra trước khi đưa vào f-string. Việc biểu diễn giá trị trong f-string chỉ chuyển đổi thành dạng chuỗi khi in ra console, không làm thay đổi kiểu dữ liệu ban đầu của biến `total_cost`.</t>
+          <t>Đáp án này sai vì nhầm lẫn chức năng giữa `sep` và `end`, đưa dấu `:` xuống cuối chuỗi và giữ khoảng trắng làm ký tự phân cách.</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>8</v>
@@ -2565,59 +2514,51 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Trong một quy trình quản lý kho hàng, lập trình viên cần tính số lượng thùng đóng gói và số sản phẩm còn dư. Đoạn mã Python 3.12 dưới đây sử dụng các toán tử số học cơ bản để xử lý:
-```python
-total_items = 17
-items_per_box = 5
-box_count = total_items // items_per_box
-remainder_items = total_items % items_per_box
-print(box_count, remainder_items)
-```
-Kết quả hiển thị trên màn hình console là gì?</t>
+          <t>Giả sử một lập trình viên đang xây dựng chương trình quản lý thông tin học viên bằng Python. Tên biến nào dưới đây tuân thủ đúng cú pháp ngôn ngữ Python 3.12 và tuân theo quy tắc đặt tên `snake_case`?</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>3.4 2</t>
+          <t>`trung-binh-diem = 8.5`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên mắc lỗi nhầm lẫn toán tử `//` (chia lấy phần nguyên) với toán tử `/` (chia số thực). Phép tính `17 / 5` mới cho ra `3.4`, còn toán tử `//` giữa hai số nguyên sẽ luôn làm tròn xuống và trả về kết quả kiểu số nguyên `int` là `3`.</t>
+          <t>`trung-binh-diem = 8.5` không hợp lệ vì dấu gạch ngang `-` được trình phiên dịch Python nhận diện là toán tử trừ số học.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>3.4 0.4</t>
+          <t>`trung_binh_diem = 8.5`</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên mắc bẫy khi nhầm lẫn cả hai toán tử: xem `//` là phép chia số thực thông thường (`17 / 5 = 3.4`) và xem `%` là phép lấy phần số thập phân còn lại sau dấu phẩy (`0.4`).</t>
+          <t>`trung_binh_diem = 8.5` là cú pháp khai báo hợp lệ vì tên biến bắt đầu bằng chữ cái, chỉ bao gồm chữ cái, chữ số và dấu gạch dưới `_`, đồng thời tuân thủ chuẩn `snake_case`.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>3 2</t>
+          <t>`trung binh diem = 8.5`</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này đúng. Toán tử `//` là phép chia lấy phần nguyên (floor division), thực hiện `17 // 5` trả về `3`. Toán tử `%` là phép chia lấy phần dư (modulo), thực hiện `17 % 5` trả về `2`. Do đó hàm `print(box_count, remainder_items)` xuất ra hai giá trị cách nhau bởi khoảng trắng là `3 2`.</t>
+          <t>`trung binh diem = 8.5` không hợp lệ vì chứa ký tự khoảng trắng giữa các từ làm sai cú pháp khai báo tên biến.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>3 0.4</t>
+          <t>`2nd_trung_binh = 8.5`</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên hiểu nhầm toán tử `%` là lấy phần thập phân của phép chia (`0.4`), trong khi bản chất toán tử `%` (modulo) trong Python là lấy phần dư số nguyên sau phép chia (`17 - 5 * 3 = 2`).</t>
+          <t>`2nd_trung_binh = 8.5` không hợp lệ vì quy tắc đặt tên định danh trong Python cấm tên biến bắt đầu bằng chữ số.</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>5</v>
@@ -2634,59 +2575,51 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 thực hiện tính toán giá trị biểu thức số học với các toán tử phối hợp dưới đây:
-```python
-base_value = 2
-multiplier = 3
-exponent = 2
-result_value = base_value + multiplier * base_value ** exponent
-print(result_value)
-```
-Giá trị của biến `result_value` được in ra màn hình console là bao nhiêu?</t>
+          <t>Trong một ứng dụng console Python, khi thực thi dòng lệnh `age = input("Nhập tuổi: ")` và người dùng nhập vào chuỗi số `25`, giá trị và kiểu dữ liệu thực tế của biến `age` nhận được là gì?</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Giá trị là `"25"` và kiểu dữ liệu là `str` (chuỗi ký tự).</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên mắc lỗi tính toán tuần tự từ trái sang phải mà không tuân theo độ ưu tiên của toán tử: lấy `base_value + multiplier` trước (`2 + 3 = 5`), sau đó nhân với `base_value` (`5 * 2 = 10`), cuối cùng lũy thừa `10 ** 2 = 100`.</t>
+          <t>Hàm `input()` trong Python mặc định luôn trả về dữ liệu thuộc kiểu chuỗi ký tự (`str`), cho dù người dùng nhập vào dữ liệu ở dạng chữ số.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Giá trị là `25` và kiểu dữ liệu là `bool` (kiểu logic).</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này đúng. Theo quy tắc độ ưu tiên của toán tử trong Python (Operator Precedence), toán tử lũy thừa `**` có độ ưu tiên cao nhất, tiếp theo là toán tử nhân `*`, và cuối cùng là toán tử cộng `+`. Thứ tự thực hiện tính toán: 1) `base_value ** exponent` tính `2 ** 2 = 4`; 2) `multiplier * 4` tính `3 * 4 = 12`; 3) `base_value + 12` tính `2 + 12 = 14`.</t>
+          <t>Kiểu `bool` đại diện cho giá trị `True` hoặc `False`, hàm `input()` không tự chuyển đổi dữ liệu nhập từ bàn phím thành kiểu logic này.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Giá trị là `25.0` và kiểu dữ liệu là `float` (số thực).</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên mắc lỗi thực hiện phép cộng trước `2 + 3 = 5`, sau đó thực hiện phép nhân với kết quả lũy thừa `2 ** 2 = 4` dẫn đến `5 * 4 = 20`, hoặc nhầm lẫn tính `(2 + 3 * 2) ** 2`. Điều này xuất phát từ việc xác định sai phạm vi tác động của toán tử lũy thừa `**`.</t>
+          <t>Kiểu dữ liệu `float` chỉ đạt được khi sử dụng hàm ép kiểu `float()`, hàm `input()` không tự động chuyển đổi chuỗi nhập vào sang số thực.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Giá trị là `25` và kiểu dữ liệu là `int` (số nguyên).</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên hiểu nhầm toán tử lũy thừa `**` là phép nhân với 2 (tức `2 * 2`), hoặc thực hiện phép toán `multiplier * base_value` trước (`3 * 2 = 6`), cộng `2 + 6 = 8`, rồi nhân 2 thành `16` thay vì tính đúng độ ưu tiên toán tử lũy thừa.</t>
+          <t>Biến `age` chỉ có kiểu dữ liệu `int` nếu giá trị từ hàm `input()` được ép kiểu chủ động bằng hàm `int()`, chẳng hạn `int(input())`.</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>5</v>
@@ -2703,59 +2636,57 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Xét đoạn mã Python 3.12 xử lý tạo mã định danh bằng các toán tử thao tác trên chuỗi và số nguyên dưới đây:
+          <t>Cho đoạn mã Python thực hiện việc hiển thị thông tin học viên như sau:
 ```python
-unit_code = "A"
-repeat_count = 3
-prefix_code = "ID-"
-final_code = prefix_code + unit_code * repeat_count
-print(final_code)
+name = "Alex"
+age = 20
+print(name + age)
 ```
-Kết quả hiển thị trên màn hình console sau khi chạy chương trình là gì?</t>
+Khi thực thi đoạn mã trên, chương trình sẽ trả về kết quả hoặc phát sinh lỗi nào dưới đây?</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ID-AID-AID-A</t>
+          <t>Trả về lỗi `TypeError` vì không thể thực hiện phép cộng trực tiếp giữa kiểu `str` và kiểu `int`.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên mắc lỗi tư duy cho rằng toán tử cộng `+` được thực hiện trước toán tử nhân `*`, dẫn đến việc nối `prefix_code + unit_code` thành `"ID-A"`, sau đó nhân 3 chuỗi này lên thành `"ID-AID-AID-A"`. Điều này vi phạm quy tắc độ ưu tiên toán tử trong Python.</t>
+          <t>Toán tử `+` trong Python không hỗ trợ tự động ép kiểu giữa chuỗi (`str`) và số nguyên (`int`), dẫn đến lỗi `TypeError`. Cần ép kiểu số nguyên sang chuỗi bằng `str(age)` trước khi nối.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>ID-AAA</t>
+          <t>In ra màn hình chuỗi `"Alex20"` sau khi trình phiên dịch tự động chuyển `age` về kiểu `str`.</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này đúng. Trong Python, toán tử `*` giữa kiểu chuỗi `str` và số nguyên `int` thực hiện phép nhân bản chuỗi (string repetition), còn toán tử `+` giữa hai chuỗi `str` thực hiện phép nối chuỗi (string concatenation). Do toán tử `*` có độ ưu tiên cao hơn toán tử `+`, biểu thức `unit_code * repeat_count` (`"A" * 3`) được tính trước tạo thành `"AAA"`. Sau đó `prefix_code + "AAA"` (`"ID-" + "AAA"`) được tính tạo ra kết quả `"ID-AAA"`.</t>
+          <t>Python là ngôn ngữ định kiểu mạnh (strongly typed), do đó không tự động ép kiểu số nguyên thành chuỗi khi thực hiện toán tử cộng `+`.</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>TypeError</t>
+          <t>Trả về lỗi `SyntaxError` do khai báo hai biến có kiểu dữ liệu khác nhau trên các dòng lệnh.</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên suy luận sai rằng Python không cho phép sử dụng toán tử `*` giữa kiểu `str` và `int`. Trong Python, toán tử `*` giữa `str` và `int` hoàn toàn hợp lệ để lặp chuỗi (ngoại lệ `TypeError` chỉ xuất hiện khi cố gắng dùng toán tử `+` giữa `str` và `int` mà không ép kiểu, hoặc dùng toán tử `*` giữa hai chuỗi `str`).</t>
+          <t>Cú pháp khai báo biến hoàn toàn đúng quy chuẩn, đây là lỗi kiểu dữ liệu (`TypeError`) xảy ra ở thời điểm thực thi câu lệnh `print` chứ không phải lỗi cú pháp `SyntaxError`.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>ID-A3</t>
+          <t>In ra màn hình chuỗi `"Alex 20"` với một ký tự khoảng trắng được tự động thêm vào giữa hai giá trị.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Giải thích chi tiết: Đáp án này sai. Học viên hiểu nhầm rằng toán tử `*` giữa chuỗi và số nguyên sẽ tự động chuyển đổi số nguyên thành chuỗi và thực hiện phép nối (`"A" + "3"`), thay vì lặp lại chuỗi đó theo số lần chỉ định.</t>
+          <t>Toán tử `+` khi thực hiện nối chuỗi không tự động chèn khoảng trắng, đồng thời chương trình đã dừng lại do lỗi kiểu dữ liệu trước khi in.</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>5</v>
@@ -2772,62 +2703,57 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã nguồn Python thực hiện các phép toán số học với thứ tự ưu tiên toán tử như sau:
+          <t>Xét đoạn mã xử lý dữ liệu nhập từ console trong Python dưới đây:
 ```python
-base_number = 17
-divider_value = 5
-result_val = base_number // divider_value + base_number % divider_value ** 2
-print(result_val)
+age_str = input("Nhập tuổi: ")
+age_num = int(age_str)
+print("Tuổi năm sau:", age_num + 1)
 ```
-Kết quả màn hình console sẽ hiển thị giá trị nào sau khi chạy chương trình?</t>
+Khi người dùng nhập chuỗi `"25"` từ bàn phím, chương trình sẽ xử lý và hiển thị kết quả như thế nào?</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>`2`</t>
+          <t>Hàm `input()` tự động chuyển chuỗi `"25"` thành số `25`, hàm `int()` gây ra lỗi `ValueError` và chương trình dừng đột ngột.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Đáp án này xuất hiện khi người học hiểu sai phép chia lấy phần dư `%` trong trường hợp `17 % 25`. Người học vô tình đảo ngược thành `25 % 17` (bằng `8`) hoặc thực hiện sai phép toán dư khi số bị chia nhỏ hơn số chia (với `17 &lt; 25` thì `17 % 25` phải bằng `17`), dẫn đến tính ra kết quả tổng cộng sai là `2`.</t>
+          <t>Hàm `input()` không tự động chuyển kiểu dữ liệu về dạng số mà luôn trả về một chuỗi (`str`). Việc gọi `int("25")` là hoàn toàn hợp lệ và không gây lỗi `ValueError`.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>`3.68`</t>
+          <t>Hàm `input()` trả về kiểu `int` mặc định, lệnh `int(age_str)` bị bỏ qua và toán tử `+` báo lỗi `TypeError` khi thực hiện phép cộng.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Đáp án này là do nhầm lẫn giữa phép chia lấy phần nguyên `//` và phép chia số thực `/`. Người học đã thực hiện phép chia thông thường `17 / 5 = 3.4` và kết hợp sai thứ tự toán tử dẫn đến kết quả trả về kiểu số thực `float` thay vì số nguyên `int`.</t>
+          <t>Hàm `input()` không mặc định trả về kiểu `int` mà luôn trả về kiểu `str`. Hàm `int()` được thực thi bình thường chứ không bị bỏ qua.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>`5`</t>
+          <t>Hàm `input()` trả về chuỗi `"25"`, hàm `int()` chuyển đổi thành số `25`, toán tử `+` tính ra `26` và in ra `Tuổi năm sau: 26`.</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Đáp án này xuất phát từ việc tính sai thứ tự ưu tiên toán tử từ trái qua phải mà không tôn trọng độ ưu tiên cao hơn của toán tử lũy thừa `**`. Người học đã lấy `base_number % divider_value` (`17 % 5 = 2`) trước, sau đó mới bình phương `2 ** 2 = 4`, rồi cộng với `17 // 5 = 3` tạo ra phép tính sai `3 + 2 = 5`.</t>
+          <t>Hàm `input()` luôn trả về kiểu dữ liệu chuỗi (`str`). Hàm `int(age_str)` sẽ ép kiểu chuỗi `"25"` thành số nguyên `25`, sau đó phép tính `25 + 1` thực hiện phép cộng số học ra `26`. Hàm `print()` tự động thêm khoảng trắng giữa các đối số và xuất ra `Tuổi năm sau: 26`.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>`20`</t>
+          <t>Hàm `input()` trả về chuỗi `"25"`, hàm `int()` không làm thay đổi kiểu dữ liệu, toán tử `+` nối chuỗi và in ra `Tuổi năm sau: 251`.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Đáp án chính xác. Trong Python, thứ tự ưu tiên của các toán tử số học từ cao xuống thấp như sau: toán tử lũy thừa `**` có độ ưu tiên cao nhất, tiếp theo là các phép toán nhân/chia/chia lấy dư/chia lấy phần nguyên (`*`, `/`, `%`, `//`), cuối cùng là cộng/trừ (`+`, `-`). Do đó:
-1. `divider_value ** 2` (`5 ** 2`) được tính trước ra `25`.
-2. Phép chia lấy phần nguyên `base_number // divider_value` (`17 // 5`) kết quả là `3`.
-3. Phép chia lấy phần dư `base_number % 25` (`17 % 25`) kết quả là `17`.
-4. Phép cộng `3 + 17` trả về kết quả cuối cùng là `20`.</t>
+          <t>Hàm `int()` trả về một giá trị số nguyên mới, do đó `age_num` mang kiểu `int`. Toán tử `+` giữa `int` và `int` là phép cộng số học chứ không phải phép nối chuỗi.</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>5</v>
@@ -2844,62 +2770,55 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Xem xét đoạn mã Python sử dụng các toán tử gán kết hợp (augmented assignment operators) dưới đây:
+          <t>Xét đoạn mã khai báo biến lưu trữ điểm số trong Python 3.12 dưới đây:
 ```python
-total_score = 40
-total_score += 10
-total_score //= 6
-total_score *= 4
-print(total_score)
+user_total_score = 95.5
 ```
-Giá trị cuối cùng của biến `total_score` được in ra màn hình là bao nhiêu?</t>
+Tên biến `user_total_score` và giá trị `95.5` tuân theo quy tắc đặt tên và thuộc kiểu dữ liệu nào trong Python?</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>`33`</t>
+          <t>Tên biến tuân thủ đúng quy chuẩn `camelCase` (viết hoa chữ cái đầu từ thứ hai) và biến nhận kiểu dữ liệu số nguyên `int`.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Đáp án này do học viên thực hiện phép chia số thực `50 / 6 = 8.333` sau đó nhân với `4` ra `33.33` rồi tự ý làm tròn thành `33`. Đây là tư duy sai vì toán tử `//=` cắt bỏ phần thập phân ngay ở bước chia chứ không làm tròn ở kết quả cuối cùng.</t>
+          <t>Quy chuẩn `camelCase` có dạng `userTotalScore` chứ không dùng dấu gạch dưới. Ngoài ra giá trị `95.5` có phần thập phân nên là kiểu `float`, không phải `int`.</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>`32`</t>
+          <t>Tên biến tuân thủ đúng quy chuẩn `PascalCase` (viết hoa toàn bộ chữ cái đầu) và biến nhận kiểu dữ liệu chuỗi `str`.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Đáp án chính xác. Đoạn mã thực hiện từng bước cập nhật biến `total_score` như sau:
-1. `total_score += 10` tương đương `total_score = 40 + 10` cập nhật biến thành `50`.
-2. `total_score //= 6` thực hiện phép chia lấy phần nguyên `50 // 6` cập nhật biến thành `8` (kiểu `int`).
-3. `total_score *= 4` thực hiện phép nhân `8 * 4` cập nhật biến thành `32`.</t>
+          <t>Quy chuẩn `PascalCase` có dạng `UserTotalScore`. Giá trị `95.5` không nằm trong dấu cọc đơn/kép nên không phải là kiểu chuỗi `str`.</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>`33.33`</t>
+          <t>Tên biến tuân thủ đúng quy chuẩn `snake_case` (chữ thường nối bằng dấu gạch dưới) và biến nhận kiểu dữ liệu số thực `float`.</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Học viên nhầm lẫn giữa toán tử chia lấy phần nguyên `//=` và toán tử chia số thực `/=`. Nếu sử dụng `/=`, phép tính `50 / 6` sẽ cho kết quả `8.3333...` và khi nhân với `4` sẽ ra `33.333...`. Tuy nhiên `//=` cắt bỏ toàn bộ phần thập phân và chỉ giữ lại giá trị nguyên `8` ngay ở bước chia.</t>
+          <t>Quy chuẩn đặt tên biến chuẩn trong Python (PEP 8) là `snake_case` (tất cả viết chữ thường, các từ phân cách bằng dấu gạch dưới `_`). Giá trị `95.5` chứa dấu chấm động nên Python tự động gán kiểu dữ liệu số thực (`float`).</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>`200`</t>
+          <t>Tên biến tuân thủ đúng quy chuẩn `kebab-case` (nối các từ bằng dấu gạch ngang) và biến nhận kiểu dữ liệu logic `bool`.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Đáp án này xuất hiện do học viên bỏ qua dòng lệnh chia `//= 6` và chỉ thực hiện phép cộng rồi nhân trực tiếp `(40 + 10) * 4 = 200`. Việc tính thiếu thao tác cập nhật làm sai lệch hoàn toàn giá trị biến.</t>
+          <t>Python không hỗ trợ quy chuẩn `kebab-case` (`user-total-score`) vì dấu gạch ngang sẽ bị hiểu nhầm là toán tử trừ `-`. Giá trị `95.5` là số thực, không phải kiểu logic `bool` (`True`/`False`).</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>5</v>
@@ -2916,61 +2835,57 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Hãy xác định kết quả xuất ra màn hình console khi thực thi đoạn mã Python kết hợp toán tử chuỗi và toán tử số học sau:
+          <t>Xét đoạn mã khởi tạo và gán lại dữ liệu cho biến trong Python 3.12 dưới đây:
 ```python
-product_code = "20"
-repeat_count = 3
-final_output = product_code * repeat_count + str(8)
-print(final_output)
+data = 100
+data = "Python 3.12"
+print("Phiên bản:", data)
 ```
-Giá trị của biến `final_output` sẽ là gì?</t>
+Chương trình trên xử lý việc thay đổi kiểu dữ liệu của biến `data` và hiển thị kết quả như thế nào?</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>`"202020.8"`</t>
+          <t>Python sử dụng kiểu dữ liệu tĩnh (static typing), việc gán chuỗi `"Python 3.12"` cho biến kiểu `int` sẽ gây ra lỗi `TypeError`.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Học viên hiểu sai rằng việc chuyển đổi `str(8)` sẽ tạo ra số thập phân dạng `.8` hoặc tự động chèn dấu chấm phân cách khi thực hiện phép nối chuỗi. Hàm `str(8)` chỉ đơn thuần chuyển số `8` thành ký tự chuỗi `"8"` mà không thêm bất kỳ ký tự đặc biệt nào.</t>
+          <t>Python không sử dụng static typing bắt buộc nên việc gán lại giá trị khác kiểu dữ liệu cho cùng một biến là hợp lệ và không báo lỗi `TypeError`.</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>`"2020208"`</t>
+          <t>Python giữ nguyên kiểu dữ liệu ban đầu `int`, bỏ qua câu lệnh gán thứ hai và xuất ra màn hình kết quả `Phiên bản: 100`.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Đáp án chính xác. Trong Python:
-1. Toán tử `*` khi dùng giữa một chuỗi `str` (`"20"`) và một số nguyên `int` (`3`) sẽ thực hiện phép lặp chuỗi (sequence repetition), tạo ra chuỗi `"202020"`.
-2. Hàm `str(8)` chuyển đổi số `8` thành chuỗi `"8"`.
-3. Toán tử `+` khi dùng giữa hai chuỗi (`"202020"` và `"8"`) sẽ thực hiện phép nối chuỗi (string concatenation), cho ra kết quả cuối cùng là `"2020208"`.</t>
+          <t>Python thực thi từ trên xuống dưới, câu lệnh gán thứ hai sẽ cập nhật lại giá trị và kiểu dữ liệu mới cho biến `data` chứ không bỏ qua.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>`"68"`</t>
+          <t>Python bắt buộc phải khai báo lại từ khóa tạo biến mới, câu lệnh gán thứ hai bị lỗi cú pháp `SyntaxError` khi biên dịch.</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Học viên lầm tưởng biến `product_code` được tự động chuyển đổi từ kiểu chuỗi sang kiểu số nguyên khi thực hiện toán tử `*`. Học viên đã tính `20 * 3 = 60`, sau đó cộng `8` thành `60 + 8 = 68` rồi gán dạng chuỗi `"68"`. Python không tự động ép kiểu chuỗi thành số trong các phép toán số học.</t>
+          <t>Python không cần từ khóa khai báo biến (như `var`, `let`, `int`), việc gán lại tên biến đã tồn tại là hoàn toàn đúng cú pháp.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>`68`</t>
+          <t>Python sử dụng kiểu dữ liệu động (dynamic typing), biến `data` được gán lại thành kiểu `str` và in ra `Phiên bản: Python 3.12`.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích sai lầm: Học viên không những nhầm lẫn toán tử lặp chuỗi `*` thành phép nhân số học (`20 * 3 = 60`) và toán tử nối chuỗi `+` thành phép cộng số học (`60 + 8 = 68`), mà còn hiểu sai kiểu dữ liệu trả về của biến `final_output` là kiểu số `int` thay vì kiểu chuỗi `str`.</t>
+          <t>Python là ngôn ngữ có kiểu dữ liệu động (dynamic typing), cho phép một biến có thể gán lại giá trị thuộc kiểu dữ liệu khác (từ `int` thành `str`) mà không gây ra lỗi. Do đó `data` mang giá trị `"Python 3.12"` và hàm `print()` xuất ra `Phiên bản: Python 3.12`.</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>5</v>
@@ -2987,60 +2902,58 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python tính toán chi phí đóng gói hàng hóa như sau:
+          <t>Trong một chương trình Python 3.12 xử lý dữ liệu đầu vào từ người dùng, lập trình viên thực thi đoạn mã sau:
 ```python
-items_count = 27
-box_capacity = 5
-full_boxes = items_count // box_capacity
-remaining_items = items_count % box_capacity
-total_cost = full_boxes * 10 + remaining_items * 3
-print(total_cost)
+val_1 = input("Nhập số thứ nhất: ")
+val_2 = input("Nhập số thứ hai: ")
+result = val_1 + val_2
+print(result)
 ```
-Kết quả in ra màn hình console sau khi chạy đoạn mã trên là gì?</t>
+Khi người dùng lần lượt nhập `10` và `20`, kết quả hiển thị trên màn hình console là gì và nguyên nhân do đâu?</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>`56.0`</t>
+          <t>Kết quả là `30` vì Python tự động nhận diện các ký tự số nhập từ bàn phím và tự động ép kiểu sang số nguyên (`int`).</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Sai vì kết quả trả về là số nguyên `56`, không phải số thực `56.0`. Học viên thường nhầm lẫn rằng phép chia trong Python luôn luôn trả về kiểu `float`. Tuy nhiên, toán tử chia lấy phần nguyên `//` giữa hai số nguyên (`int`) sẽ trả về kết quả kiểu `int`.</t>
+          <t>Python là ngôn ngữ định kiểu động nhưng không tự động chuyển đổi kiểu dữ liệu chuỗi số sang số nguyên khi nhập liệu từ hàm `input()`. Người dùng bắt buộc phải dùng các hàm ép kiểu như `int()` để tính toán.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>`41`</t>
+          <t>Kết quả là `1020` vì hàm `input()` luôn trả về kiểu dữ liệu chuỗi (`str`), do đó toán tử `+` thực hiện ghép hai chuỗi lại với nhau.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Sai do học viên nhầm lẫn vai trò của toán tử chia lấy phần nguyên `//` và toán tử chia lấy phần dư `%` (tưởng rằng `full_boxes` nhận giá trị `2` và `remaining_items` nhận giá trị `5`), dẫn đến tính toán sai thành `2 * 10 + 5 * 3 = 35` hoặc tính sai thứ tự ưu tiên của các toán tử số học.</t>
+          <t>Trong Python, tất cả dữ liệu thu thập được từ hàm `input()` đều mang kiểu dữ liệu chuỗi (`str`). Khi áp dụng toán tử `+` giữa hai giá trị dạng chuỗi, Python sẽ thực hiện thao tác nối chuỗi chứ không tính toán số học, dẫn đến chuỗi kết quả `1020`.</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>`57.2`</t>
+          <t>Chương trình báo lỗi `TypeError` vì toán tử `+` không được phép sử dụng trực tiếp giữa hai chuỗi ký tự thu thập từ `input()`.</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Sai vì đây là kết quả khi học viên nhầm lẫn giữa toán tử chia thực `/` và toán tử chia lấy phần nguyên `//`. Nếu lấy `27 / 5 = 5.4`, biểu thức sẽ trở thành `5.4 * 10 + ... = 54 + ...` làm sai lệch kết quả số lượng thùng hàng nguyên cần tính toán.</t>
+          <t>Phép cộng hai chuỗi ký tự trong Python là thao tác hoàn toàn hợp lệ và trả về chuỗi mới thu được bằng cách ghép nối hai chuỗi thành phần.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>`56`</t>
+          <t>Kết quả là `10 20` vì hàm `input()` mặc định tự động thêm một ký tự khoảng trắng vào giữa các giá trị được nối.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì toán tử chia lấy phần nguyên `//` thực hiện `27 // 5` thu được `5` (kiểu `int`). Toán tử chia lấy phần dư `%` thực hiện `27 % 5` thu được `2` (kiểu `int`). Biểu thức tính tổng chi phí `total_cost = 5 * 10 + 2 * 3 = 50 + 6 = 56`. Cả hai toán tử này đều làm việc trên số nguyên và trả về kết quả số nguyên `56`.</t>
+          <t>Toán tử `+` dùng trên hai chuỗi sẽ ghép sát các ký tự của chuỗi thứ hai vào ngay sau chuỗi thứ nhất chứ không tự động thêm bất kỳ khoảng trắng nào.</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>7</v>
@@ -3057,55 +2970,47 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Trong Python, toán tử gán phức hợp (compound assignment operators) tuân theo quy tắc ưu tiên tính toán biểu thức ở vế phải trước khi thực hiện phép gán. Cho đoạn mã sau:
-```python
-base_score = 10
-multiplier = 3
-base_score *= multiplier + 2
-base_score **= 2
-print(base_score)
-```
-Giá trị được in ra màn hình console là bao nhiêu?</t>
+          <t>Khi khai báo các biến để lưu trữ thông tin trong ứng dụng Python 3.12, câu lệnh khởi tạo nào dưới đây sẽ gây ra lỗi cú pháp (`SyntaxError`) do vi phạm quy tắc đặt tên biến?</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>`2500`</t>
+          <t>`2nd_user_score = 95` vì tên biến trong Python tuyệt đối không được phép bắt đầu bằng một chữ số.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì trong biểu thức gán phức hợp `base_score *= multiplier + 2`, biểu thức vế phải `multiplier + 2` được ưu tiên tính trước, cho ra `3 + 2 = 5`. Lệnh này tương đương `base_score = 10 * 5 = 50`. Tiếp theo, câu lệnh `base_score **= 2` thực hiện phép lũy thừa `50 ** 2 = 2500` và gán lại cho `base_score`.</t>
+          <t>Quy tắc đặt tên biến trong Python quy định tên biến có thể chứa chữ cái, chữ số và dấu gạch dưới `_`, nhưng ký tự đầu tiên của tên biến không được phép là một chữ số. Việc bắt đầu tên biến bằng số `2` sẽ khiến trình biên dịch báo lỗi `SyntaxError`.</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>`1024`</t>
+          <t>`UserScore = 95` vì quy tắc của Python bắt buộc tất cả tên biến phải được viết hoàn toàn bằng ký tự thường.</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Sai do hiểu sai quy tắc ưu tiên biểu thức của toán tử gán phức hợp. Học viên thường tưởng rằng `base_score *= multiplier + 2` sẽ tương đương với `(base_score * multiplier) + 2`, tức `(10 * 3) + 2 = 32`, sau đó lấy `32 ** 2 = 1024`. Thực tế, vế phải `multiplier + 2` luôn được tính xong hoàn chỉnh trước khi thực hiện toán tử `*=`.</t>
+          <t>Python phân biệt chữ hoa và chữ thường (case-sensitive) nhưng không cấm đặt tên biến có ký tự viết hoa. Cú pháp `UserScore = 95` vẫn hoàn toàn hợp lệ.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>`100`</t>
+          <t>`_user_score_2 = 95` vì tên biến trong Python không được phép bắt đầu hoặc kết thúc bằng dấu gạch dưới.</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Sai do học viên nhầm lẫn thứ tự thực thi hoặc bỏ qua câu lệnh gán phức hợp `base_score *= multiplier + 2`, chỉ lấy giá trị ban đầu `base_score = 10` để thực hiện lũy thừa `10 ** 2 = 100`.</t>
+          <t>Đặt tên biến bắt đầu hoặc kết thúc bằng dấu gạch dưới `_` là đúng cú pháp trong Python và được sử dụng rộng rãi trong nhiều chuẩn thiết kế mã nguồn.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>`900`</t>
+          <t>`user_score = 95` vì tên biến không được phép chứa ký tự gạch dưới để nối giữa các từ đơn.</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Sai do học viên bỏ sót toán tử cộng `+ 2` ở vế phải của câu lệnh đầu tiên, chỉ tính `base_score *= 3` dẫn đến `base_score = 30`, sau đó lấy `30 ** 2 = 900`.</t>
+          <t>Ký tự gạch dưới `_` là hợp lệ và đại diện cho chuẩn đặt tên snake_case được khuyến nghị phổ biến trong Python.</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
@@ -3126,64 +3031,58 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python xử lý phép toán số học và toán tử so sánh sau:
+          <t>Xét đoạn mã Python 3.12 thực hiện chuyển đổi kiểu dữ liệu cơ bản dưới đây:
 ```python
-number_a = 7 / 2
-number_b = 7 // 2
-is_equal = number_a == number_b
-diff_value = number_a - number_b
-print(is_equal)
-print(diff_value)
+x = int(8.9)
+y = str(x)
+z = float(y)
+print(type(z), z)
 ```
-Kết quả in ra màn hình console là gì?</t>
+Kết quả in ra màn hình console sau khi thực thi đoạn mã trên là gì?</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>`False`
-`1`</t>
+          <t>`&lt;class 'float'&gt; 8.9` vì hàm `int(8.9)` tự động làm tròn số thực lên giá trị gần nhất trước khi chuyển đổi tiếp.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Sai do học viên tính đúng kết quả của phép so sánh `is_equal` là `False`, nhưng nhầm lẫn kết quả của phép trừ `number_a - number_b` với toán tử chia lấy phần dư `7 % 2` (kết quả phần dư là `1`), thay vì thực hiện phép trừ số thực `3.5 - 3 = 0.5`.</t>
+          <t>Hàm `int()` khi ép kiểu từ số thực sang số nguyên không thực hiện làm tròn số mà cắt bỏ hoàn toàn phần thập phân, do đó giá trị thu được sau `int(8.9)` phải là `8` chứ không giữ được `.9`.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>`True`
-`0`</t>
+          <t>`&lt;class 'float'&gt; 8.0` vì `int(8.9)` lấy phần nguyên là `8`, sau đó chuyển thành chuỗi `"8"` và cuối cùng ép kiểu sang float thành `8.0`.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Sai vì học viên nhầm lẫn rằng toán tử chia thực `/` trong Python 3 sẽ làm tròn số nguyên giống như phép chia `//` (cho rằng cả hai đều bằng `3`). Thực tế, toán tử `/` trong Python luôn trả về số thực (`3.5`), nên phép so sánh `3.5 == 3` không thể bằng `True` và hiệu `3.5 - 3` không thể bằng `0`.</t>
+          <t>Khi truyền số thực `8.9` vào hàm `int()`, Python cắt bỏ phần thập phân và giữ lại số nguyên `8`. Hàm `str(8)` chuyển số nguyên này thành chuỗi `"8"`. Cuối cùng, hàm `float("8")` chuyển chuỗi này thành giá trị số thực `8.0` thuộc lớp `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>`False`
-`0.5`</t>
+          <t>`&lt;class 'str'&gt; 8.0` vì biến trung gian `y` mang kiểu chuỗi nên kết quả gán cuối cùng cho `z` vẫn duy trì kiểu chuỗi.</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì toán tử chia thực `/` trả về kết quả kiểu `float` là `number_a = 3.5`. Toán tử chia lấy phần nguyên `//` trả về kết quả kiểu `int` là `number_b = 3`. Biểu thức so sánh `3.5 == 3` cho kết quả `False`. Phép trừ giữa số thực và số nguyên `3.5 - 3` trả về kết quả số thực `0.5`.</t>
+          <t>Hàm `float()` nhận đầu vào là chuỗi `"8"` và trả về một đối tượng số thực `8.0`. Do vậy `type(z)` phải trả về lớp `&lt;class 'float'&gt;`, không phải `&lt;class 'str'&gt;`.</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>`True`
-`0.5`</t>
+          <t>`&lt;class 'int'&gt; 8` vì giá trị được khởi tạo ban đầu qua hàm `int()` nên các bước chuyển đổi về sau giữ nguyên kiểu nguyên.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Sai do học viên tính đúng hiệu số `diff_value` là `0.5` nhưng đánh giá sai phép so sánh `is_equal`. Hai giá trị `3.5` và `3` là khác nhau về mặt giá trị số học nên toán tử `==` bắt buộc trả về `False` chứ không thể là `True`.</t>
+          <t>Biến `z` nhận kết quả của phép chuyển đổi `float(y)`. Do đó, kiểu dữ liệu của `z` bị thay đổi thành `&lt;class 'float'&gt;` thay vì giữ nguyên kiểu `int` ban đầu.</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>7</v>
@@ -3200,60 +3099,55 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Trong một hệ thống phân tích dữ liệu log, lập trình viên muốn quy đổi tổng số giây `total_seconds = 3665` thành số giờ, số phút và số giây còn lại bằng các toán tử số học trong Python 3.12. Đoạn mã được viết như sau:
+          <t>Trong ngôn ngữ lập trình Python 3.12, khi thực hiện dòng lệnh:
 ```python
-total_seconds = 3665
-hours = total_seconds // 3600
-remaining_seconds = total_seconds % 3600
-minutes = remaining_seconds // 60
-seconds = remaining_seconds % 60
-print(f"{hours}:{minutes}:{seconds}")
+length = input("Nhập chiều dài: ")
 ```
-Kết quả xuất ra màn hình console là gì?</t>
+Nếu người dùng nhập vào giá trị `15` từ màn hình console, kiểu dữ liệu thực tế của biến `length` là gì và bản chất hoạt động của lệnh này được giải thích như thế nào?</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>1:1:5</t>
+          <t>Biến `length` thuộc kiểu `NoneType`, vì hàm `input()` chỉ thực hiện lệnh ghi nhận thao tác nhập mà không trả về giá trị nào.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Toán tử chia lấy phần nguyên `//` tính `3665 // 3600` cho kết quả `1` (giờ). Toán tử chia lấy phần dư `%` tính `3665 % 3600` thu được `65` (giây còn lại). Tiếp theo, `65 // 60` cho kết quả `1` (phút) và `65 % 60` cho kết quả `5` (giây). Định dạng f-string in ra đúng chuỗi `1:1:5`.</t>
+          <t>Hàm `input()` trả về giá trị là chuỗi dữ liệu do người dùng nhập vào console, không phải trả về giá trị `None` (kiểu `NoneType`).</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.018:1.083:5</t>
+          <t>Biến `length` thuộc kiểu `int`, vì Python 3.12 tự động kiểm tra cú pháp và ép chuỗi chữ số `"15"` về kiểu số nguyên.</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên nhầm lẫn giữa toán tử chia lấy phần nguyên `//` và toán tử chia số thực `/`. Nếu sử dụng `/`, kết quả phép chia `3665 / 3600` sẽ tạo ra số thực `1.0180555...` thay vì số nguyên `1`.</t>
+          <t>Python không tự động ép kiểu dữ liệu chuỗi số sang số nguyên khi dùng hàm `input()`. Muốn thu được kiểu `int`, lập trình viên phải thực hiện ép kiểu thủ công thông qua hàm `int()`.</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1:1:65</t>
+          <t>Biến `length` thuộc kiểu `float`, vì Python mặc định coi các số nhập vào từ bàn phím là số thực để đảm bảo độ chính xác.</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy cú pháp và logic: Học viên tính đúng số phút nhưng quên thực hiện toán tử chia lấy phần dư `% 60` ở bước cuối cùng để quy đổi 65 giây còn lại thành 5 giây, mà giữ nguyên giá trị `65` ban đầu.</t>
+          <t>Python không mặc định chuyển đổi dữ liệu nhập vào thành kiểu `float`. Hàm `input()` luôn trả về kiểu `str`, nếu muốn kiểu số thực cần gọi hàm `float()` một cách chủ động.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>1:65:5</t>
+          <t>Biến `length` thuộc kiểu `str`, vì hàm `input()` luôn trả về giá trị là một chuỗi ký tự bất kể dữ liệu người dùng nhập là số hay chữ.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên mắc lỗi logic khi không thực hiện phép chia lấy phần nguyên `// 60` cho biến `remaining_seconds` mà gán trực tiếp giá trị `65` vào biến `minutes`, dẫn đến số phút vượt quá 60.</t>
+          <t>Hàm `input()` trong Python có cơ chế mặc định là đọc toàn bộ dữ liệu từ chuẩn đầu vào (console) dưới dạng một chuỗi ký tự (`str`). Ngay cả khi người dùng nhập chuỗi số `15`, giá trị lưu trong biến `length` vẫn là `"15"` (kiểu `str`).</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>7</v>
@@ -3270,63 +3164,56 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Xem xét đoạn mã Python thực thi tính toán biểu thức số học kết hợp giữa toán tử lũy thừa `**` và toán tử gán phức hợp `+=` dưới đây:
+          <t>Xét đoạn mã nguồn khởi tạo và gán giá trị biến trong Python 3.12 như sau:
 ```python
-base_value = 2
-multiplier = 3
-result = base_value ** multiplier + 4 * 2
-result += base_value
-print(result)
+x = 100
+x = "Rikkei Academy"
 ```
-Giá trị của biến `result` được in ra console là bao nhiêu?</t>
+Kết quả thực thi đoạn mã trên và nguyên lý hoạt động về kiểu dữ liệu của biến trong Python được mô tả như thế nào?</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Đoạn mã gây ra lỗi thực thi (TypeError), vì việc đổi kiểu dữ liệu cho biến trong Python đòi hỏi phải dùng từ khóa khai báo lại biến.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên tính đúng giá trị của biểu thức ban đầu `2 ** 3 + 4 * 2 = 16` nhưng bỏ qua dòng lệnh gán phức hợp `result += base_value` ở bước tiếp theo.</t>
+          <t>Python không yêu cầu bất kỳ từ khóa khai báo biến nào (như `var`, `let`, `int`) và cho phép gán lại giá trị khác kiểu trực tiếp mà không xảy ra lỗi `TypeError`.</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Đoạn mã gây ra lỗi biên dịch (SyntaxError), vì biến `x` đã được cố định kiểu dữ liệu là số nguyên (`int`) ở dòng lệnh đầu tiên.</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy cú pháp: Học viên nhầm lẫn giữa toán tử lũy thừa `**` và toán tử nhân `*`, tính `2 ** 3` thành `2 * 3 = 6`. Sau đó tính `6 + 8 = 14` nên cho ra kết quả sai.</t>
+          <t>Python không phải là ngôn ngữ định kiểu tĩnh (Static Typing). Biến không gắn chặt với một kiểu dữ liệu cố định ngay từ khi khởi tạo nên không phát sinh lỗi biên dịch khi gán giá trị thuộc kiểu khác.</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>Đoạn mã chạy thành công và `x` chuyển sang kiểu `str`, vì Python áp dụng cơ chế định kiểu động (Dynamic Typing) cho phép biến thay đổi kiểu dữ liệu theo giá trị được gán.</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên hiểu sai thứ tự ưu tiên của toán tử, cho rằng phép cộng `multiplier + 4` (3 + 4 = 7) được tính trước lũy thừa, dẫn đến việc tính `2 ** 7 = 128` rồi mới nhân `2` thành `256`.</t>
+          <t>Python là ngôn ngữ định kiểu động (Dynamic Typing). Biến trong Python chỉ là một nhãn tham chiếu đến đối tượng dữ liệu. Khi gán `x = "Rikkei Academy"`, biến `x` sẽ tham chiếu đến chuỗi mới và tự động cập nhật kiểu dữ liệu sang `str` mà không gây lỗi.</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Đoạn mã thực thi thành công nhưng biến `x` vẫn giữ kiểu `int`, đồng thời giá trị chuỗi `"Rikkei Academy"` bị bỏ qua.</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Theo quy tắc ưu tiên toán tử trong Python:
-1. Toán tử lũy thừa `**` thực hiện trước: `2 ** 3 = 8`.
-2. Toán tử nhân `*` thực hiện tiếp theo: `4 * 2 = 8`.
-3. Toán tử cộng `+` thực hiện sau: `8 + 8 = 16`.
-4. Toán tử gán phức hợp `+=` thực hiện cuối cùng: `result = 16 + 2 = 18`.</t>
+          <t>Lệnh gán sau sẽ ghi đè tham chiếu của biến `x` lên giá trị mới. Biến `x` sẽ lưu giá trị chuỗi mới và mang kiểu `str`, không giữ lại kiểu `int` ban đầu.</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>7</v>
@@ -3343,63 +3230,58 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Trong Python, các toán tử số học như `*` và `+` có thể áp dụng cho kiểu dữ liệu chuỗi (`str`). Hãy xác định kết quả xuất ra màn hình console của đoạn mã sau:
+          <t>Khi cần tính tổng hai số nguyên nhập từ console trong Python 3.12, đoạn mã sau được thực thi:
 ```python
-unit_code = "A"
-repeat_count = 3
-prefix = unit_code * repeat_count
-suffix = "10"
-result = prefix + suffix * 2
+a = input()
+b = input()
+result = int(a) + int(b)
 print(result)
 ```
-Kết quả in ra là gì?</t>
+Nếu người dùng lần lượt nhập vào console hai giá trị `20` và `30`, màn hình sẽ hiển thị kết quả nào và nguyên lý ép kiểu ở đây là gì?</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>AAA20</t>
+          <t>Hiển thị `"50"`, vì mọi kết quả khi đưa vào hàm `print()` đều tự động chuyển đổi thành chuỗi và giữ nguyên dấu ngoặc kép khi in.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên nhầm lẫn rằng chuỗi `"10"` sẽ tự động chuyển đổi kiểu dữ liệu thành số nguyên `10` để thực hiện phép nhân số học `10 * 2 = 20` rồi mới nối vào chuỗi `"AAA"`.</t>
+          <t>Hàm `print()` chuyển đổi giá trị thành định dạng hiển thị ra console nhưng không in ra dấu ngoặc kép đại diện cho chuỗi ký tự.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>AAA10AAA10</t>
+          <t>Hiển thị `2030`, vì hàm `int()` chỉ có tác dụng kiểm tra định dạng số chứ không làm thay đổi bản chất nối chuỗi của phép toán `+`.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên hiểu sai thứ tự ưu tiên toán tử, cho rằng phép cộng chuỗi `prefix + suffix` thực hiện trước ra `"AAA10"`, sau đó mới nhân `2` để tạo thành `"AAA10AAA10"`.</t>
+          <t>Phép cộng `+` đối với hai số nguyên (`int`) sẽ thực hiện tính tổng số học. Phép nối chuỗi chỉ xảy ra khi cộng hai đối tượng kiểu `str` (tức là `a + b` thay vì `int(a) + int(b)`).</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>AAAAAA10</t>
+          <t>Hiển thị `50`, vì hàm `int()` thực hiện chuyển đổi hai chuỗi ký tự `"20"` và `"30"` thành hai số nguyên `20` và `30` trước khi thực hiện phép cộng số học.</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai. Phân tích bẫy tư duy: Học viên tính sai logic lặp chuỗi khi cho rằng toán tử nhân ở biến `suffix` vô tình nhân đôi số lần lặp của biến `prefix` từ 3 lên 6 lần thành `"AAAAAA"`.</t>
+          <t>Hàm `input()` trả về chuỗi ký tự `"20"` và `"30"`. Việc bọc `int(a)` và `int(b)` giúp chuyển đổi dữ liệu từ dạng chuỗi (`str`) sang số nguyên (`int`), cho phép phép toán `+` thực hiện tính tổng số học thành `50`.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>AAA1010</t>
+          <t>Hiển thị `50.0`, vì phép cộng giữa hai biến sau khi thực hiện ép kiểu trong Python 3.12 luôn tự động quy đổi về kiểu số thực (`float`).</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng. Trong Python:
-1. Phép nhân chuỗi `"A" * 3` tạo ra chuỗi lặp lại `"AAA"`.
-2. Phép nhân chuỗi `"10" * 2` có độ ưu tiên cao hơn phép cộng, tạo ra chuỗi `"1010"`.
-3. Phép cộng chuỗi `"AAA" + "1010"` thực hiện nối chuỗi tạo thành `"AAA1010"`.</t>
+          <t>Phép cộng giữa hai số nguyên (`int + int`) trong Python luôn trả về một số nguyên (`int`), do đó kết quả là `50` chứ không phải số thực `50.0`.</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>7</v>
@@ -3416,60 +3298,59 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 xử lý toán tử số học với số nguyên âm dưới đây:
+          <t>Phân tích đoạn mã nguồn Python 3.12 thực hiện khai báo biến và ép kiểu dữ liệu từ chuỗi nhập vào như sau:
 ```python
-first_num = -17
-second_num = 5
-result_div = first_num // second_num
-result_mod = first_num % second_num
-output_text = f"{result_div}:{result_mod}"
-print(output_text)
+x = "25"
+y = "4"
+z = float(x) / int(y)
+output = str(z)
+print(output, type(z))
 ```
-Kết quả hiển thị ra màn hình console sau khi chạy đoạn mã trên là gì?</t>
+Kết quả hiển thị chính xác ra màn hình console là gì?</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>"-4:3"</t>
+          <t>Giá trị hiển thị là `6.25 &lt;class 'int'&gt;` vì biến `y` có kiểu `int` chiếm ưu tiên chuyển đổi trong phép tính số học.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì trong Python, toán tử chia lấy phần nguyên `//` thực hiện làm tròn xuống số nguyên nhỏ hơn hoặc bằng giá trị thực (floor division). Ta có `-17 / 5 = -3.4`, làm tròn xuống thành `-4`. Toán tử lấy phần dư `%` tuân theo công thức toán học `a % b = a - (a // b) * b`, do đó `-17 - (-4 * 5) = -17 - (-20) = 3`. Kết quả thu được là `"-4:3"`.</t>
+          <t>Khi thực hiện phép tính số học giữa `float` và `int`, Python nâng cấp kiểu dữ liệu của kết quả thành `float`, không bị hạ về kiểu `int`.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>"-3:3"</t>
+          <t>Giá trị hiển thị là `6.25 &lt;class 'str'&gt;` vì biến `output` đã ép kiểu `z` về chuỗi khiến kiểu của `z` bị thay đổi theo.</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên xác định đúng phần dư là `3` theo quy tắc toán học Python nhưng lại tính sai thương số `result_div`. Người học đã tính `-17 // 5` bằng cách cắt bỏ phần thập phân ra `-3` (thay vì làm tròn xuống `-4`), dẫn đến kết quả thương số không khớp với phép tính phần dư.</t>
+          <t>Hàm `str(z)` tạo ra một đối tượng chuỗi mới gán cho `output` chứ không biến đổi kiểu dữ liệu của biến `z`. Do đó `type(z)` vẫn là `&lt;class 'float'&gt;`.</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>"-4:-2"</t>
+          <t>Giá trị hiển thị là `6 &lt;class 'int'&gt;` vì khi chia số thực cho số nguyên Python tự động làm tròn thành số nguyên.</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên xác định đúng thương số `result_div = -4` theo quy tắc làm tròn xuống của Python, nhưng lại áp dụng sai công thức tính phần dư `%` khi giữ nguyên dấu âm của số bị chia (`-17 % 5 = -2`). Trong Python, dấu của kết quả phép `%` luôn cùng dấu với số chia (`second_num = 5` là số dương).</t>
+          <t>Phép chia toán học `/` trong Python không tự động ép kiểu về số nguyên hay làm tròn; kết quả của phép chia `/` luôn luôn có kiểu `float`.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>"-3:-2"</t>
+          <t>Giá trị hiển thị là `6.25 &lt;class 'float'&gt;` vì phép chia `/` tạo kết quả kiểu `float` và biến `z` vẫn giữ kiểu dữ liệu gốc.</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên nhầm lẫn cơ chế chia phần nguyên của Python với các ngôn ngữ như C/C++/Java (vốn cắt bỏ phần thập phân - truncation towards zero). Nếu cắt bỏ phần thập phân, `-17 / 5` sẽ ra `-3` và phần dư tương ứng là `-2`. Trong Python, phép chia `//` luôn làm tròn xuống vô cực âm.</t>
+          <t>Trong Python 3.12, phép chia `/` giữa hai số luôn trả về một số thực kiểu `float` (25.0 / 4 = 6.25). Việc gọi hàm `str(z)` để tạo ra biến `output` chỉ trả về một chuỗi mới mà không làm thay đổi kiểu dữ liệu ban đầu của biến `z` (`&lt;class 'float'&gt;`).</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>9</v>
@@ -3486,57 +3367,57 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 thực hiện các phép toán lũy thừa và toán tử đổi dấu như sau:
+          <t>Xét đoạn mã nguồn Python 3.12 thực thi các thao tác khai báo biến, phép toán trên chuỗi và chuyển đổi kiểu dữ liệu cơ sở:
 ```python
-base_val = 2
-exp_val_1 = 3
-exp_val_2 = 2
-result_pow = base_val ** exp_val_1 ** exp_val_2
-result_neg = -base_val ** exp_val_1
-output_text = f"{result_pow}_{result_neg}"
-print(output_text)
+var_a = "12.5"
+var_b = "2"
+num_a = float(var_a)
+num_b = int(var_b)
+res_1 = num_a * num_b
+res_2 = var_a * num_b
+print(res_1, len(res_2))
 ```
-Kết quả in ra màn hình console là gì?</t>
+Kết quả in ra màn hình của chương trình trên là gì?</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>"64_8"</t>
+          <t>Kết quả in ra là `25 4` do kết quả nhân số thực bị làm tròn thành `25` và chuỗi chỉ lưu giữ độ dài của bản sao đầu.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên mắc đồng thời hai bẫy cú pháp: vừa nhầm lẫn tính kết hợp của toán tử lũy thừa `**` là từ trái sang phải (`(2 ** 3) ** 2 = 64`), vừa xác định sai độ ưu tiên toán tử dấu âm khiến giá trị `result_neg` bị đổi thành số dương `8`.</t>
+          <t>Phép nhân số thực không bị cắt phần thập phân và phép nhân chuỗi nhân bản số ký tự thực tế nên kết quả `25 4` là hoàn toàn sai.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>"512_-8"</t>
+          <t>Kết quả in ra là `25.0 8` do phép nhân số thực tạo ra `25.0` và nhân chuỗi tạo ra `"12.512.5"` có độ dài 8.</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì: (1) Toán tử lũy thừa `**` trong Python có tính kết hợp từ phải sang trái (right-associative). Do đó, `2 ** 3 ** 2` được tính thành `2 ** (3 ** 2) = 2 ** 9 = 512`. (2) Toán tử lũy thừa `**` có độ ưu tiên cao hơn toán tử một ngôi `-`, nên `-2 ** 3` được thực thi thành `-(2 ** 3) = -8`. Kết quả chuỗi kết hợp thu được là `"512_-8"`.</t>
+          <t>Trong Python 3.12, khi nhân số thực `12.5` với số nguyên `2`, kết quả `res_1` nhận kiểu `float` với giá trị `25.0`. Phép nhân chuỗi `"12.5" * 2` thực hiện lặp chuỗi thành `"12.512.5"`, do đó `len(res_2)` trả về độ dài bằng 8.</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>"512_8"</t>
+          <t>Kết quả in ra là `25.0 4` do phép nhân số thực ra `25.0` nhưng phép nhân chuỗi không làm thay đổi độ dài ban đầu.</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên áp dụng sai độ ưu tiên toán tử, cho rằng toán tử đổi dấu một ngôi `-` có độ ưu tiên cao hơn toán tử lũy thừa `**`. Khi đó `-2 ** 3` bị tính nhầm thành `(-2) ** 3` rồi tiếp tục tính sai dấu của phép mũ lẻ thành số dương `8`.</t>
+          <t>Phép nhân chuỗi ký tự `"12.5" * 2` nhân bản chuỗi hai lần tạo thành chuỗi mới có độ dài là 8, không giữ nguyên độ dài 4.</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>"64_-8"</t>
+          <t>Kết quả in ra là `25 8` do phép nhân hai số được tự động ép về số nguyên `25` và nhân chuỗi tạo độ dài 8.</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên nhầm lẫn toán tử lũy thừa `**` có tính kết hợp từ trái sang phải như các toán tử số học thông thường (`+`, `-`, `*`, `/`). Nếu tính từ trái sang phải, `(2 ** 3) ** 2` sẽ ra `8 ** 2 = 64`, đây là bẫy phổ biến về tính kết hợp (associativity) toán tử trong Python.</t>
+          <t>Phép nhân giữa `float` và `int` không tự động chuyển kết quả về kiểu `int`, do đó `res_1` có giá trị là `25.0` chứ không phải `25`.</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
@@ -3557,61 +3438,59 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Cho đoạn mã Python 3.12 thực hiện chuỗi phép toán chia và nhân với các số nguyên dưới đây:
+          <t>Thực hiện đoạn mã Python 3.12 xử lý chuyển đổi kiểu dữ liệu Boolean và chuỗi ký tự như sau:
 ```python
-val_a = 7
-val_b = 2
-val_c = 4
-result_val = val_a / val_b * val_c
-result_int = val_a // val_b * val_c
-output_text = f"{result_val}_{result_int}"
-print(output_text)
+val1 = "True"
+val2 = bool(val1)
+val3 = bool("")
+output = str(val2) + str(val3)
+print(output, type(val3))
 ```
-Kết quả hiển thị ra màn hình console sau khi chương trình thực thi là gì?</t>
+Kết quả xuất ra màn hình console chính xác là gì?</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>"14.0_12"</t>
+          <t>Output là `TrueFalse &lt;class 'str'&gt;` vì khi gọi hàm `str(val3)` để tạo `output` thì biến `val3` bị đổi kiểu thành chuỗi.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Đáp án đúng vì: (1) Phép chia thực `/` trong Python luôn trả về kiểu số thực `float`. Toán tử `/` và `*` có cùng độ ưu tiên và kết hợp từ trái sang phải, nên `7 / 2 * 4` = `3.5 * 4 = 14.0`. (2) Phép chia lấy phần nguyên `//` trên hai số nguyên dương trả về kiểu `int`, `7 // 2` = `3`, sau đó `3 * 4 = 12`. Kết quả hiển thị qua f-string là `"14.0_12"`.</t>
+          <t>Việc gọi hàm `str(val3)` chỉ sử dụng giá trị của `val3` để trả về một chuỗi mới mà không làm thay đổi kiểu dữ liệu thực tế của biến `val3` (`&lt;class 'bool'&gt;`).</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>"0.875_12"</t>
+          <t>Output là `TrueFalse &lt;class 'bool'&gt;` vì `bool("True")` trả về `True`, `bool("")` trả về `False` và `val3` thuộc kiểu `bool`.</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên áp dụng sai độ ưu tiên toán tử, thực hiện phép nhân `val_b * val_c` (`2 * 4 = 8`) trước phép chia, dẫn đến `7 / 8 = 0.875`. Trong Python, toán tử `/` và `*` có độ ưu tiên ngang nhau nên phải ưu tiên thực hiện từ trái sang phải.</t>
+          <t>Trong Python 3.12, `bool("True")` trả về `True` (do chuỗi không rỗng) và `bool("")` trả về `False` (do chuỗi rỗng). Phép cộng chuỗi `str(val2) + str(val3)` ghép hai chuỗi thành `"TrueFalse"`. Hàm `type(val3)` xác định đúng kiểu dữ liệu nguyên bản là `&lt;class 'bool'&gt;`.</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>"14.0_14.0"</t>
+          <t>Output là `10 &lt;class 'int'&gt;` vì các giá trị Boolean `True` và `False` khi cộng lại sẽ được ép kiểu thành số `1` và `0`.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên nhầm lẫn rằng phép nhân `*` theo sau phép chia phần nguyên `//` sẽ tự động chuyển đổi kiểu dữ liệu toàn bộ biểu thức thành số thực `float`. Thực tế, `7 // 2` trả về số nguyên `3`, và `3 * 4` giữ nguyên kiểu số nguyên `12`.</t>
+          <t>Phép cộng được thực hiện trên hai chuỗi `str(val2)` và `str(val3)` là phép nối chuỗi ký tự chứ không phải phép cộng số học giữa hai số nguyên.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>"14_12"</t>
+          <t>Output là `TrueTrue &lt;class 'bool'&gt;` vì mọi chuỗi ký tự khi chuyển đổi qua `bool()` đều mặc định trả về giá trị `True`.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Đáp án sai do học viên không nắm rõ đặc tính của toán tử chia thực `/` trong Python. Trong Python 3, phép chia `/` luôn luôn trả về kết quả thuộc kiểu số thực (`float`), kể cả khi phép chia chia hết hoặc tất cả toán hạng là số nguyên (`14.0` thay vì `14`).</t>
+          <t>Chuỗi rỗng `""` khi ép kiểu qua `bool()` luôn trả về `False` chứ không phải `True`.</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>9</v>
